--- a/research/traditional_assets/database/data/bulgaria/bulgaria_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_engineering_construction.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09601059129832248</v>
+        <v>0.09595508070702417</v>
       </c>
       <c r="C2">
-        <v>131.2371178601662</v>
+        <v>130.0788671762094</v>
       </c>
       <c r="D2">
-        <v>125.8971178601662</v>
+        <v>125.9738671762094</v>
       </c>
       <c r="E2">
-        <v>-47.7</v>
+        <v>-46.465</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.235</v>
       </c>
       <c r="G2">
         <v>5.34</v>
@@ -1451,28 +1451,28 @@
         <v>11.95</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0621205</v>
       </c>
       <c r="N2">
-        <v>11.95</v>
+        <v>11.8878795</v>
       </c>
       <c r="O2">
-        <v>1.195</v>
+        <v>1.18878795</v>
       </c>
       <c r="P2">
-        <v>10.755</v>
+        <v>10.69909155</v>
       </c>
       <c r="Q2">
-        <v>14.505</v>
+        <v>14.44909155</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09601059129832248</v>
+        <v>0.09646705121921634</v>
       </c>
       <c r="T2">
-        <v>0.776741878503467</v>
+        <v>0.783803168308044</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>192.3680588533576</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09595508070702417</v>
+        <v>0.09589957011572585</v>
       </c>
       <c r="C3">
-        <v>130.0788671762094</v>
+        <v>128.9207101250654</v>
       </c>
       <c r="D3">
-        <v>125.9738671762094</v>
+        <v>126.0507101250654</v>
       </c>
       <c r="E3">
-        <v>-46.465</v>
+        <v>-45.23</v>
       </c>
       <c r="F3">
-        <v>1.235</v>
+        <v>2.47</v>
       </c>
       <c r="G3">
         <v>5.34</v>
@@ -1533,28 +1533,28 @@
         <v>11.95</v>
       </c>
       <c r="M3">
-        <v>0.0621205</v>
+        <v>0.124241</v>
       </c>
       <c r="N3">
-        <v>11.8878795</v>
+        <v>11.825759</v>
       </c>
       <c r="O3">
-        <v>1.18878795</v>
+        <v>1.1825759</v>
       </c>
       <c r="P3">
-        <v>10.69909155</v>
+        <v>10.6431831</v>
       </c>
       <c r="Q3">
-        <v>14.44909155</v>
+        <v>14.3931831</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09646705121921634</v>
+        <v>0.09693282664869984</v>
       </c>
       <c r="T3">
-        <v>0.783803168308044</v>
+        <v>0.7910085660678163</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>192.3680588533576</v>
+        <v>96.18402942667879</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09589957011572585</v>
+        <v>0.09584405952442752</v>
       </c>
       <c r="C4">
-        <v>128.9207101250654</v>
+        <v>127.7626468781845</v>
       </c>
       <c r="D4">
-        <v>126.0507101250654</v>
+        <v>126.1276468781845</v>
       </c>
       <c r="E4">
-        <v>-45.23</v>
+        <v>-43.995</v>
       </c>
       <c r="F4">
-        <v>2.47</v>
+        <v>3.705</v>
       </c>
       <c r="G4">
         <v>5.34</v>
@@ -1615,28 +1615,28 @@
         <v>11.95</v>
       </c>
       <c r="M4">
-        <v>0.124241</v>
+        <v>0.1863615</v>
       </c>
       <c r="N4">
-        <v>11.825759</v>
+        <v>11.7636385</v>
       </c>
       <c r="O4">
-        <v>1.1825759</v>
+        <v>1.17636385</v>
       </c>
       <c r="P4">
-        <v>10.6431831</v>
+        <v>10.58727465</v>
       </c>
       <c r="Q4">
-        <v>14.3931831</v>
+        <v>14.33727465</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09693282664869984</v>
+        <v>0.0974082056952861</v>
       </c>
       <c r="T4">
-        <v>0.7910085660678163</v>
+        <v>0.798362528729852</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>96.18402942667879</v>
+        <v>64.12268628445253</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09584405952442752</v>
+        <v>0.0957885489331292</v>
       </c>
       <c r="C5">
-        <v>127.7626468781845</v>
+        <v>126.6046776074356</v>
       </c>
       <c r="D5">
-        <v>126.1276468781845</v>
+        <v>126.2046776074356</v>
       </c>
       <c r="E5">
-        <v>-43.995</v>
+        <v>-42.76000000000001</v>
       </c>
       <c r="F5">
-        <v>3.705</v>
+        <v>4.94</v>
       </c>
       <c r="G5">
         <v>5.34</v>
@@ -1697,28 +1697,28 @@
         <v>11.95</v>
       </c>
       <c r="M5">
-        <v>0.1863615</v>
+        <v>0.248482</v>
       </c>
       <c r="N5">
-        <v>11.7636385</v>
+        <v>11.701518</v>
       </c>
       <c r="O5">
-        <v>1.17636385</v>
+        <v>1.1701518</v>
       </c>
       <c r="P5">
-        <v>10.58727465</v>
+        <v>10.5313662</v>
       </c>
       <c r="Q5">
-        <v>14.33727465</v>
+        <v>14.2813662</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0974082056952861</v>
+        <v>0.09789348847200958</v>
       </c>
       <c r="T5">
-        <v>0.798362528729852</v>
+        <v>0.8058696989473471</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.12268628445253</v>
+        <v>48.0920147133394</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0957885489331292</v>
+        <v>0.09573303834183088</v>
       </c>
       <c r="C6">
-        <v>126.6046776074356</v>
+        <v>125.446802485108</v>
       </c>
       <c r="D6">
-        <v>126.2046776074356</v>
+        <v>126.281802485108</v>
       </c>
       <c r="E6">
-        <v>-42.76000000000001</v>
+        <v>-41.52500000000001</v>
       </c>
       <c r="F6">
-        <v>4.94</v>
+        <v>6.175000000000001</v>
       </c>
       <c r="G6">
         <v>5.34</v>
@@ -1779,28 +1779,28 @@
         <v>11.95</v>
       </c>
       <c r="M6">
-        <v>0.248482</v>
+        <v>0.3106025</v>
       </c>
       <c r="N6">
-        <v>11.701518</v>
+        <v>11.6393975</v>
       </c>
       <c r="O6">
-        <v>1.1701518</v>
+        <v>1.16393975</v>
       </c>
       <c r="P6">
-        <v>10.5313662</v>
+        <v>10.47545775</v>
       </c>
       <c r="Q6">
-        <v>14.2813662</v>
+        <v>14.22545775</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09789348847200958</v>
+        <v>0.09838898772824303</v>
       </c>
       <c r="T6">
-        <v>0.8058696989473471</v>
+        <v>0.8135349148536312</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.0920147133394</v>
+        <v>38.47361177067152</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09573303834183088</v>
+        <v>0.09567752775053255</v>
       </c>
       <c r="C7">
-        <v>125.446802485108</v>
+        <v>124.289021683912</v>
       </c>
       <c r="D7">
-        <v>126.281802485108</v>
+        <v>126.359021683912</v>
       </c>
       <c r="E7">
-        <v>-41.52500000000001</v>
+        <v>-40.29000000000001</v>
       </c>
       <c r="F7">
-        <v>6.175000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="G7">
         <v>5.34</v>
@@ -1861,28 +1861,28 @@
         <v>11.95</v>
       </c>
       <c r="M7">
-        <v>0.3106025</v>
+        <v>0.372723</v>
       </c>
       <c r="N7">
-        <v>11.6393975</v>
+        <v>11.577277</v>
       </c>
       <c r="O7">
-        <v>1.16393975</v>
+        <v>1.1577277</v>
       </c>
       <c r="P7">
-        <v>10.47545775</v>
+        <v>10.4195493</v>
       </c>
       <c r="Q7">
-        <v>14.22545775</v>
+        <v>14.1695493</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09838898772824303</v>
+        <v>0.09889502952184315</v>
       </c>
       <c r="T7">
-        <v>0.8135349148536312</v>
+        <v>0.8213632204600492</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.47361177067152</v>
+        <v>32.06134314222626</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09567752775053255</v>
+        <v>0.09562201715923423</v>
       </c>
       <c r="C8">
-        <v>124.289021683912</v>
+        <v>123.1313353769809</v>
       </c>
       <c r="D8">
-        <v>126.359021683912</v>
+        <v>126.4363353769809</v>
       </c>
       <c r="E8">
-        <v>-40.29000000000001</v>
+        <v>-39.05500000000001</v>
       </c>
       <c r="F8">
-        <v>7.41</v>
+        <v>8.645</v>
       </c>
       <c r="G8">
         <v>5.34</v>
@@ -1943,28 +1943,28 @@
         <v>11.95</v>
       </c>
       <c r="M8">
-        <v>0.372723</v>
+        <v>0.4348434999999999</v>
       </c>
       <c r="N8">
-        <v>11.577277</v>
+        <v>11.5151565</v>
       </c>
       <c r="O8">
-        <v>1.1577277</v>
+        <v>1.15151565</v>
       </c>
       <c r="P8">
-        <v>10.4195493</v>
+        <v>10.36364085</v>
       </c>
       <c r="Q8">
-        <v>14.1695493</v>
+        <v>14.11364085</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09889502952184315</v>
+        <v>0.09941195393466046</v>
       </c>
       <c r="T8">
-        <v>0.8213632204600492</v>
+        <v>0.8293598767246695</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.06134314222626</v>
+        <v>27.48115126476537</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09562201715923424</v>
+        <v>0.0955665065679359</v>
       </c>
       <c r="C9">
-        <v>123.1313353769809</v>
+        <v>121.973743737872</v>
       </c>
       <c r="D9">
-        <v>126.4363353769809</v>
+        <v>126.513743737872</v>
       </c>
       <c r="E9">
-        <v>-39.055</v>
+        <v>-37.82</v>
       </c>
       <c r="F9">
-        <v>8.645000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G9">
         <v>5.34</v>
@@ -2025,28 +2025,28 @@
         <v>11.95</v>
       </c>
       <c r="M9">
-        <v>0.4348435</v>
+        <v>0.496964</v>
       </c>
       <c r="N9">
-        <v>11.5151565</v>
+        <v>11.453036</v>
       </c>
       <c r="O9">
-        <v>1.15151565</v>
+        <v>1.1453036</v>
       </c>
       <c r="P9">
-        <v>10.36364085</v>
+        <v>10.3077324</v>
       </c>
       <c r="Q9">
-        <v>14.11364085</v>
+        <v>14.0577324</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09941195393466047</v>
+        <v>0.09994011583471293</v>
       </c>
       <c r="T9">
-        <v>0.8293598767246697</v>
+        <v>0.8375303733428687</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.48115126476537</v>
+        <v>24.04600735666969</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0955665065679359</v>
+        <v>0.09551099597663759</v>
       </c>
       <c r="C10">
-        <v>121.973743737872</v>
+        <v>120.8162469405677</v>
       </c>
       <c r="D10">
-        <v>126.513743737872</v>
+        <v>126.5912469405677</v>
       </c>
       <c r="E10">
-        <v>-37.82</v>
+        <v>-36.585</v>
       </c>
       <c r="F10">
-        <v>9.880000000000001</v>
+        <v>11.115</v>
       </c>
       <c r="G10">
         <v>5.34</v>
@@ -2107,28 +2107,28 @@
         <v>11.95</v>
       </c>
       <c r="M10">
-        <v>0.496964</v>
+        <v>0.5590845</v>
       </c>
       <c r="N10">
-        <v>11.453036</v>
+        <v>11.3909155</v>
       </c>
       <c r="O10">
-        <v>1.1453036</v>
+        <v>1.13909155</v>
       </c>
       <c r="P10">
-        <v>10.3077324</v>
+        <v>10.25182395</v>
       </c>
       <c r="Q10">
-        <v>14.0577324</v>
+        <v>14.00182395</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09994011583471293</v>
+        <v>0.1004798856886127</v>
       </c>
       <c r="T10">
-        <v>0.8375303733428687</v>
+        <v>0.8458804413153139</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.04600735666969</v>
+        <v>21.37422876148418</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09551099597663759</v>
+        <v>0.09545548538533927</v>
       </c>
       <c r="C11">
-        <v>120.8162469405677</v>
+        <v>119.6588451594772</v>
       </c>
       <c r="D11">
-        <v>126.5912469405677</v>
+        <v>126.6688451594772</v>
       </c>
       <c r="E11">
-        <v>-36.585</v>
+        <v>-35.35</v>
       </c>
       <c r="F11">
-        <v>11.115</v>
+        <v>12.35</v>
       </c>
       <c r="G11">
         <v>5.34</v>
@@ -2189,28 +2189,28 @@
         <v>11.95</v>
       </c>
       <c r="M11">
-        <v>0.5590845</v>
+        <v>0.6212049999999999</v>
       </c>
       <c r="N11">
-        <v>11.3909155</v>
+        <v>11.328795</v>
       </c>
       <c r="O11">
-        <v>1.13909155</v>
+        <v>1.1328795</v>
       </c>
       <c r="P11">
-        <v>10.25182395</v>
+        <v>10.1959155</v>
       </c>
       <c r="Q11">
-        <v>14.00182395</v>
+        <v>13.9459155</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1004798856886127</v>
+        <v>0.1010316504281547</v>
       </c>
       <c r="T11">
-        <v>0.8458804413153139</v>
+        <v>0.8544160663538137</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.37422876148418</v>
+        <v>19.23680588533576</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09545548538533927</v>
+        <v>0.09539997479404094</v>
       </c>
       <c r="C12">
-        <v>119.6588451594772</v>
+        <v>118.5015385694374</v>
       </c>
       <c r="D12">
-        <v>126.6688451594772</v>
+        <v>126.7465385694374</v>
       </c>
       <c r="E12">
-        <v>-35.35</v>
+        <v>-34.115</v>
       </c>
       <c r="F12">
-        <v>12.35</v>
+        <v>13.585</v>
       </c>
       <c r="G12">
         <v>5.34</v>
@@ -2271,28 +2271,28 @@
         <v>11.95</v>
       </c>
       <c r="M12">
-        <v>0.621205</v>
+        <v>0.6833255</v>
       </c>
       <c r="N12">
-        <v>11.328795</v>
+        <v>11.2666745</v>
       </c>
       <c r="O12">
-        <v>1.1328795</v>
+        <v>1.12666745</v>
       </c>
       <c r="P12">
-        <v>10.1959155</v>
+        <v>10.14000705</v>
       </c>
       <c r="Q12">
-        <v>13.9459155</v>
+        <v>13.89000705</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1010316504281547</v>
+        <v>0.1015958143753269</v>
       </c>
       <c r="T12">
-        <v>0.8544160663538137</v>
+        <v>0.8631435031909312</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.23680588533576</v>
+        <v>17.48800535030523</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09539997479404094</v>
+        <v>0.09534446420274263</v>
       </c>
       <c r="C13">
-        <v>118.5015385694374</v>
+        <v>117.3443273457146</v>
       </c>
       <c r="D13">
-        <v>126.7465385694374</v>
+        <v>126.8243273457146</v>
       </c>
       <c r="E13">
-        <v>-34.115</v>
+        <v>-32.88</v>
       </c>
       <c r="F13">
-        <v>13.585</v>
+        <v>14.82</v>
       </c>
       <c r="G13">
         <v>5.34</v>
@@ -2353,28 +2353,28 @@
         <v>11.95</v>
       </c>
       <c r="M13">
-        <v>0.6833255</v>
+        <v>0.7454459999999999</v>
       </c>
       <c r="N13">
-        <v>11.2666745</v>
+        <v>11.204554</v>
       </c>
       <c r="O13">
-        <v>1.12666745</v>
+        <v>1.1204554</v>
       </c>
       <c r="P13">
-        <v>10.14000705</v>
+        <v>10.0840986</v>
       </c>
       <c r="Q13">
-        <v>13.89000705</v>
+        <v>13.8340986</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1015958143753269</v>
+        <v>0.1021728002303894</v>
       </c>
       <c r="T13">
-        <v>0.8631435031909312</v>
+        <v>0.8720692908652562</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.48800535030523</v>
+        <v>16.03067157111313</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09534446420274263</v>
+        <v>0.09528895361144429</v>
       </c>
       <c r="C14">
-        <v>117.3443273457146</v>
+        <v>116.1872116640055</v>
       </c>
       <c r="D14">
-        <v>126.8243273457146</v>
+        <v>126.9022116640055</v>
       </c>
       <c r="E14">
-        <v>-32.88</v>
+        <v>-31.645</v>
       </c>
       <c r="F14">
-        <v>14.82</v>
+        <v>16.055</v>
       </c>
       <c r="G14">
         <v>5.34</v>
@@ -2435,28 +2435,28 @@
         <v>11.95</v>
       </c>
       <c r="M14">
-        <v>0.7454459999999999</v>
+        <v>0.8075665</v>
       </c>
       <c r="N14">
-        <v>11.204554</v>
+        <v>11.1424335</v>
       </c>
       <c r="O14">
-        <v>1.1204554</v>
+        <v>1.11424335</v>
       </c>
       <c r="P14">
-        <v>10.0840986</v>
+        <v>10.02819015</v>
       </c>
       <c r="Q14">
-        <v>13.8340986</v>
+        <v>13.77819015</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1021728002303894</v>
+        <v>0.1027630501280969</v>
       </c>
       <c r="T14">
-        <v>0.8720692908652562</v>
+        <v>0.8812002690608297</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.03067157111313</v>
+        <v>14.79754298871981</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09528895361144429</v>
+        <v>0.09523344302014598</v>
       </c>
       <c r="C15">
-        <v>116.1872116640055</v>
+        <v>115.0301917004387</v>
       </c>
       <c r="D15">
-        <v>126.9022116640055</v>
+        <v>126.9801917004387</v>
       </c>
       <c r="E15">
-        <v>-31.645</v>
+        <v>-30.41</v>
       </c>
       <c r="F15">
-        <v>16.055</v>
+        <v>17.29</v>
       </c>
       <c r="G15">
         <v>5.34</v>
@@ -2517,28 +2517,28 @@
         <v>11.95</v>
       </c>
       <c r="M15">
-        <v>0.8075665</v>
+        <v>0.8696870000000001</v>
       </c>
       <c r="N15">
-        <v>11.1424335</v>
+        <v>11.080313</v>
       </c>
       <c r="O15">
-        <v>1.11424335</v>
+        <v>1.1080313</v>
       </c>
       <c r="P15">
-        <v>10.02819015</v>
+        <v>9.972281699999998</v>
       </c>
       <c r="Q15">
-        <v>13.77819015</v>
+        <v>13.7222817</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1027630501280969</v>
+        <v>0.1033670267676116</v>
       </c>
       <c r="T15">
-        <v>0.8812002690608297</v>
+        <v>0.8905435955865331</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.79754298871981</v>
+        <v>13.74057563238268</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09523344302014598</v>
+        <v>0.09538043242884767</v>
       </c>
       <c r="C16">
-        <v>115.0301917004387</v>
+        <v>113.5889130280484</v>
       </c>
       <c r="D16">
-        <v>126.9801917004387</v>
+        <v>126.7739130280484</v>
       </c>
       <c r="E16">
-        <v>-30.41</v>
+        <v>-29.175</v>
       </c>
       <c r="F16">
-        <v>17.29</v>
+        <v>18.525</v>
       </c>
       <c r="G16">
         <v>5.34</v>
@@ -2599,45 +2599,45 @@
         <v>11.95</v>
       </c>
       <c r="M16">
-        <v>0.8696870000000001</v>
+        <v>0.9595950000000001</v>
       </c>
       <c r="N16">
-        <v>11.080313</v>
+        <v>10.990405</v>
       </c>
       <c r="O16">
-        <v>1.1080313</v>
+        <v>1.0990405</v>
       </c>
       <c r="P16">
-        <v>9.972281699999998</v>
+        <v>9.8913645</v>
       </c>
       <c r="Q16">
-        <v>13.7222817</v>
+        <v>13.6413645</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1033670267676116</v>
+        <v>0.1039852146221737</v>
       </c>
       <c r="T16">
-        <v>0.8905435955865331</v>
+        <v>0.9001067650893119</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.1</v>
       </c>
       <c r="W16">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.74057563238268</v>
+        <v>12.45317034790719</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09538043242884767</v>
+        <v>0.09533842183754933</v>
       </c>
       <c r="C17">
-        <v>113.5889130280484</v>
+        <v>112.4128004690905</v>
       </c>
       <c r="D17">
-        <v>126.7739130280484</v>
+        <v>126.8328004690905</v>
       </c>
       <c r="E17">
-        <v>-29.175</v>
+        <v>-27.94</v>
       </c>
       <c r="F17">
-        <v>18.525</v>
+        <v>19.76</v>
       </c>
       <c r="G17">
         <v>5.34</v>
@@ -2681,28 +2681,28 @@
         <v>11.95</v>
       </c>
       <c r="M17">
-        <v>0.9595949999999999</v>
+        <v>1.023568</v>
       </c>
       <c r="N17">
-        <v>10.990405</v>
+        <v>10.926432</v>
       </c>
       <c r="O17">
-        <v>1.0990405</v>
+        <v>1.0926432</v>
       </c>
       <c r="P17">
-        <v>9.8913645</v>
+        <v>9.833788799999999</v>
       </c>
       <c r="Q17">
-        <v>13.6413645</v>
+        <v>13.5837888</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1039852146221737</v>
+        <v>0.1046181212351778</v>
       </c>
       <c r="T17">
-        <v>0.9001067650893119</v>
+        <v>0.9098976291040614</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.45317034790719</v>
+        <v>11.67484720116299</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09533842183754933</v>
+        <v>0.095296411246251</v>
       </c>
       <c r="C18">
-        <v>112.4128004690905</v>
+        <v>111.2367426428794</v>
       </c>
       <c r="D18">
-        <v>126.8328004690905</v>
+        <v>126.8917426428794</v>
       </c>
       <c r="E18">
-        <v>-27.94</v>
+        <v>-26.705</v>
       </c>
       <c r="F18">
-        <v>19.76</v>
+        <v>20.995</v>
       </c>
       <c r="G18">
         <v>5.34</v>
@@ -2763,28 +2763,28 @@
         <v>11.95</v>
       </c>
       <c r="M18">
-        <v>1.023568</v>
+        <v>1.087541</v>
       </c>
       <c r="N18">
-        <v>10.926432</v>
+        <v>10.862459</v>
       </c>
       <c r="O18">
-        <v>1.0926432</v>
+        <v>1.0862459</v>
       </c>
       <c r="P18">
-        <v>9.833788799999999</v>
+        <v>9.7762131</v>
       </c>
       <c r="Q18">
-        <v>13.5837888</v>
+        <v>13.5262131</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1046181212351778</v>
+        <v>0.105266278609941</v>
       </c>
       <c r="T18">
-        <v>0.9098976291040614</v>
+        <v>0.9199244175529013</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.67484720116299</v>
+        <v>10.98809148344752</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.095296411246251</v>
+        <v>0.09525440065495268</v>
       </c>
       <c r="C19">
-        <v>111.2367426428794</v>
+        <v>110.0607396257575</v>
       </c>
       <c r="D19">
-        <v>126.8917426428794</v>
+        <v>126.9507396257575</v>
       </c>
       <c r="E19">
-        <v>-26.705</v>
+        <v>-25.47</v>
       </c>
       <c r="F19">
-        <v>20.995</v>
+        <v>22.23</v>
       </c>
       <c r="G19">
         <v>5.34</v>
@@ -2845,28 +2845,28 @@
         <v>11.95</v>
       </c>
       <c r="M19">
-        <v>1.087541</v>
+        <v>1.151514</v>
       </c>
       <c r="N19">
-        <v>10.862459</v>
+        <v>10.798486</v>
       </c>
       <c r="O19">
-        <v>1.0862459</v>
+        <v>1.0798486</v>
       </c>
       <c r="P19">
-        <v>9.7762131</v>
+        <v>9.718637399999999</v>
       </c>
       <c r="Q19">
-        <v>13.5262131</v>
+        <v>13.4686374</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.105266278609941</v>
+        <v>0.1059302447011618</v>
       </c>
       <c r="T19">
-        <v>0.9199244175529013</v>
+        <v>0.9301957618175666</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.98809148344752</v>
+        <v>10.37764195658932</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09525440065495268</v>
+        <v>0.09521239006365437</v>
       </c>
       <c r="C20">
-        <v>110.0607396257575</v>
+        <v>108.884791494209</v>
       </c>
       <c r="D20">
-        <v>126.9507396257575</v>
+        <v>127.009791494209</v>
       </c>
       <c r="E20">
-        <v>-25.47</v>
+        <v>-24.235</v>
       </c>
       <c r="F20">
-        <v>22.23</v>
+        <v>23.465</v>
       </c>
       <c r="G20">
         <v>5.34</v>
@@ -2927,28 +2927,28 @@
         <v>11.95</v>
       </c>
       <c r="M20">
-        <v>1.151514</v>
+        <v>1.215487</v>
       </c>
       <c r="N20">
-        <v>10.798486</v>
+        <v>10.734513</v>
       </c>
       <c r="O20">
-        <v>1.0798486</v>
+        <v>1.0734513</v>
       </c>
       <c r="P20">
-        <v>9.718637399999999</v>
+        <v>9.661061699999999</v>
       </c>
       <c r="Q20">
-        <v>13.4686374</v>
+        <v>13.4110617</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1059302447011618</v>
+        <v>0.1066106050168572</v>
       </c>
       <c r="T20">
-        <v>0.9301957618175666</v>
+        <v>0.9407207195208656</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.37764195658932</v>
+        <v>9.83145027466357</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09521239006365437</v>
+        <v>0.09547637947235604</v>
       </c>
       <c r="C21">
-        <v>108.884791494209</v>
+        <v>107.2796261667158</v>
       </c>
       <c r="D21">
-        <v>127.009791494209</v>
+        <v>126.6396261667158</v>
       </c>
       <c r="E21">
-        <v>-24.235</v>
+        <v>-23</v>
       </c>
       <c r="F21">
-        <v>23.465</v>
+        <v>24.7</v>
       </c>
       <c r="G21">
         <v>5.34</v>
@@ -3009,45 +3009,45 @@
         <v>11.95</v>
       </c>
       <c r="M21">
-        <v>1.215487</v>
+        <v>1.32145</v>
       </c>
       <c r="N21">
-        <v>10.734513</v>
+        <v>10.62855</v>
       </c>
       <c r="O21">
-        <v>1.0734513</v>
+        <v>1.062855</v>
       </c>
       <c r="P21">
-        <v>9.661061699999999</v>
+        <v>9.565694999999998</v>
       </c>
       <c r="Q21">
-        <v>13.4110617</v>
+        <v>13.315695</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1066106050168572</v>
+        <v>0.107307974340445</v>
       </c>
       <c r="T21">
-        <v>0.9407207195208656</v>
+        <v>0.9515088011667471</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>9.83145027466357</v>
+        <v>9.043096598433536</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09547637947235604</v>
+        <v>0.09544966888105771</v>
       </c>
       <c r="C22">
-        <v>107.2796261667158</v>
+        <v>106.0819815536583</v>
       </c>
       <c r="D22">
-        <v>126.6396261667158</v>
+        <v>126.6769815536583</v>
       </c>
       <c r="E22">
-        <v>-23</v>
+        <v>-21.765</v>
       </c>
       <c r="F22">
-        <v>24.7</v>
+        <v>25.935</v>
       </c>
       <c r="G22">
         <v>5.34</v>
@@ -3091,28 +3091,28 @@
         <v>11.95</v>
       </c>
       <c r="M22">
-        <v>1.32145</v>
+        <v>1.3875225</v>
       </c>
       <c r="N22">
-        <v>10.62855</v>
+        <v>10.5624775</v>
       </c>
       <c r="O22">
-        <v>1.062855</v>
+        <v>1.05624775</v>
       </c>
       <c r="P22">
-        <v>9.565694999999998</v>
+        <v>9.506229749999999</v>
       </c>
       <c r="Q22">
-        <v>13.315695</v>
+        <v>13.25622975</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.107307974340445</v>
+        <v>0.1080229985836174</v>
       </c>
       <c r="T22">
-        <v>0.9515088011667471</v>
+        <v>0.9625699988036635</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.043096598433536</v>
+        <v>8.612472950889085</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09544966888105771</v>
+        <v>0.0954229582897594</v>
       </c>
       <c r="C23">
-        <v>106.0819815536583</v>
+        <v>104.8843589848331</v>
       </c>
       <c r="D23">
-        <v>126.6769815536583</v>
+        <v>126.7143589848331</v>
       </c>
       <c r="E23">
-        <v>-21.765</v>
+        <v>-20.53</v>
       </c>
       <c r="F23">
-        <v>25.935</v>
+        <v>27.17</v>
       </c>
       <c r="G23">
         <v>5.34</v>
@@ -3173,28 +3173,28 @@
         <v>11.95</v>
       </c>
       <c r="M23">
-        <v>1.3875225</v>
+        <v>1.453595</v>
       </c>
       <c r="N23">
-        <v>10.5624775</v>
+        <v>10.496405</v>
       </c>
       <c r="O23">
-        <v>1.05624775</v>
+        <v>1.0496405</v>
       </c>
       <c r="P23">
-        <v>9.506229749999999</v>
+        <v>9.446764499999999</v>
       </c>
       <c r="Q23">
-        <v>13.25622975</v>
+        <v>13.1967645</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1080229985836174</v>
+        <v>0.1087563567817428</v>
       </c>
       <c r="T23">
-        <v>0.9625699988036635</v>
+        <v>0.9739148168928086</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.612472950889085</v>
+        <v>8.220996907666853</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0954229582897594</v>
+        <v>0.09539624769846108</v>
       </c>
       <c r="C24">
-        <v>104.8843589848331</v>
+        <v>103.6867584797591</v>
       </c>
       <c r="D24">
-        <v>126.7143589848331</v>
+        <v>126.7517584797591</v>
       </c>
       <c r="E24">
-        <v>-20.53</v>
+        <v>-19.295</v>
       </c>
       <c r="F24">
-        <v>27.17</v>
+        <v>28.405</v>
       </c>
       <c r="G24">
         <v>5.34</v>
@@ -3255,28 +3255,28 @@
         <v>11.95</v>
       </c>
       <c r="M24">
-        <v>1.453595</v>
+        <v>1.5196675</v>
       </c>
       <c r="N24">
-        <v>10.496405</v>
+        <v>10.4303325</v>
       </c>
       <c r="O24">
-        <v>1.0496405</v>
+        <v>1.04303325</v>
       </c>
       <c r="P24">
-        <v>9.446764499999999</v>
+        <v>9.387299249999998</v>
       </c>
       <c r="Q24">
-        <v>13.1967645</v>
+        <v>13.13729925</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1087563567817428</v>
+        <v>0.1095087632447546</v>
       </c>
       <c r="T24">
-        <v>0.9739148168928086</v>
+        <v>0.9855543055816718</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.220996907666853</v>
+        <v>7.863562259507424</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09539624769846108</v>
+        <v>0.09554233710716274</v>
       </c>
       <c r="C25">
-        <v>103.6867584797591</v>
+        <v>102.2474771732128</v>
       </c>
       <c r="D25">
-        <v>126.7517584797591</v>
+        <v>126.5474771732128</v>
       </c>
       <c r="E25">
-        <v>-19.295</v>
+        <v>-18.06</v>
       </c>
       <c r="F25">
-        <v>28.405</v>
+        <v>29.64</v>
       </c>
       <c r="G25">
         <v>5.34</v>
@@ -3337,45 +3337,45 @@
         <v>11.95</v>
       </c>
       <c r="M25">
-        <v>1.5196675</v>
+        <v>1.609452</v>
       </c>
       <c r="N25">
-        <v>10.4303325</v>
+        <v>10.340548</v>
       </c>
       <c r="O25">
-        <v>1.04303325</v>
+        <v>1.0340548</v>
       </c>
       <c r="P25">
-        <v>9.387299249999998</v>
+        <v>9.306493199999998</v>
       </c>
       <c r="Q25">
-        <v>13.13729925</v>
+        <v>13.0564932</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1095087632447546</v>
+        <v>0.1102809698778457</v>
       </c>
       <c r="T25">
-        <v>0.9855543055816718</v>
+        <v>0.9975000966044524</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.1</v>
       </c>
       <c r="W25">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.863562259507424</v>
+        <v>7.424887477228273</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09554233710716274</v>
+        <v>0.09552282651586443</v>
       </c>
       <c r="C26">
-        <v>102.2474771732128</v>
+        <v>101.0397213264183</v>
       </c>
       <c r="D26">
-        <v>126.5474771732128</v>
+        <v>126.5747213264184</v>
       </c>
       <c r="E26">
-        <v>-18.06</v>
+        <v>-16.825</v>
       </c>
       <c r="F26">
-        <v>29.64</v>
+        <v>30.875</v>
       </c>
       <c r="G26">
         <v>5.34</v>
@@ -3419,28 +3419,28 @@
         <v>11.95</v>
       </c>
       <c r="M26">
-        <v>1.609452</v>
+        <v>1.6765125</v>
       </c>
       <c r="N26">
-        <v>10.340548</v>
+        <v>10.2734875</v>
       </c>
       <c r="O26">
-        <v>1.0340548</v>
+        <v>1.02734875</v>
       </c>
       <c r="P26">
-        <v>9.306493199999998</v>
+        <v>9.24613875</v>
       </c>
       <c r="Q26">
-        <v>13.0564932</v>
+        <v>12.99613875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1102809698778457</v>
+        <v>0.1110737686878192</v>
       </c>
       <c r="T26">
-        <v>0.9975000966044524</v>
+        <v>1.009764442054507</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.424887477228273</v>
+        <v>7.127891978139143</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09552282651586443</v>
+        <v>0.09550331592456611</v>
       </c>
       <c r="C27">
-        <v>101.0397213264183</v>
+        <v>99.83197721282842</v>
       </c>
       <c r="D27">
-        <v>126.5747213264184</v>
+        <v>126.6019772128284</v>
       </c>
       <c r="E27">
-        <v>-16.825</v>
+        <v>-15.59</v>
       </c>
       <c r="F27">
-        <v>30.875</v>
+        <v>32.11</v>
       </c>
       <c r="G27">
         <v>5.34</v>
@@ -3501,28 +3501,28 @@
         <v>11.95</v>
       </c>
       <c r="M27">
-        <v>1.6765125</v>
+        <v>1.743573</v>
       </c>
       <c r="N27">
-        <v>10.2734875</v>
+        <v>10.206427</v>
       </c>
       <c r="O27">
-        <v>1.02734875</v>
+        <v>1.0206427</v>
       </c>
       <c r="P27">
-        <v>9.24613875</v>
+        <v>9.1857843</v>
       </c>
       <c r="Q27">
-        <v>12.99613875</v>
+        <v>12.9357843</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1110737686878192</v>
+        <v>0.1118879944926569</v>
       </c>
       <c r="T27">
-        <v>1.009764442054507</v>
+        <v>1.022360256300509</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.127891978139143</v>
+        <v>6.853742286672253</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09550331592456611</v>
+        <v>0.09548380533326781</v>
       </c>
       <c r="C28">
-        <v>99.83197721282842</v>
+        <v>98.62424484002429</v>
       </c>
       <c r="D28">
-        <v>126.6019772128284</v>
+        <v>126.6292448400243</v>
       </c>
       <c r="E28">
-        <v>-15.59</v>
+        <v>-14.355</v>
       </c>
       <c r="F28">
-        <v>32.11</v>
+        <v>33.345</v>
       </c>
       <c r="G28">
         <v>5.34</v>
@@ -3583,28 +3583,28 @@
         <v>11.95</v>
       </c>
       <c r="M28">
-        <v>1.743573</v>
+        <v>1.8106335</v>
       </c>
       <c r="N28">
-        <v>10.206427</v>
+        <v>10.1393665</v>
       </c>
       <c r="O28">
-        <v>1.0206427</v>
+        <v>1.01393665</v>
       </c>
       <c r="P28">
-        <v>9.1857843</v>
+        <v>9.12542985</v>
       </c>
       <c r="Q28">
-        <v>12.9357843</v>
+        <v>12.87542985</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1118879944926569</v>
+        <v>0.1127245278537915</v>
       </c>
       <c r="T28">
-        <v>1.022360256300509</v>
+        <v>1.035301161347772</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.853742286672253</v>
+        <v>6.599899979758465</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09548380533326781</v>
+        <v>0.09546429474196946</v>
       </c>
       <c r="C29">
-        <v>98.62424484002429</v>
+        <v>97.41652421559388</v>
       </c>
       <c r="D29">
-        <v>126.6292448400243</v>
+        <v>126.6565242155939</v>
       </c>
       <c r="E29">
-        <v>-14.355</v>
+        <v>-13.12</v>
       </c>
       <c r="F29">
-        <v>33.345</v>
+        <v>34.58000000000001</v>
       </c>
       <c r="G29">
         <v>5.34</v>
@@ -3665,28 +3665,28 @@
         <v>11.95</v>
       </c>
       <c r="M29">
-        <v>1.8106335</v>
+        <v>1.877694</v>
       </c>
       <c r="N29">
-        <v>10.1393665</v>
+        <v>10.072306</v>
       </c>
       <c r="O29">
-        <v>1.01393665</v>
+        <v>1.0072306</v>
       </c>
       <c r="P29">
-        <v>9.12542985</v>
+        <v>9.0650754</v>
       </c>
       <c r="Q29">
-        <v>12.87542985</v>
+        <v>12.8150754</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1127245278537915</v>
+        <v>0.1135842982527354</v>
       </c>
       <c r="T29">
-        <v>1.035301161347772</v>
+        <v>1.048601535979681</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.599899979758465</v>
+        <v>6.364189266195662</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09546429474196946</v>
+        <v>0.09544478415067113</v>
       </c>
       <c r="C30">
-        <v>97.41652421559388</v>
+        <v>96.20881534713152</v>
       </c>
       <c r="D30">
-        <v>126.6565242155939</v>
+        <v>126.6838153471315</v>
       </c>
       <c r="E30">
-        <v>-13.12</v>
+        <v>-11.885</v>
       </c>
       <c r="F30">
-        <v>34.58000000000001</v>
+        <v>35.815</v>
       </c>
       <c r="G30">
         <v>5.34</v>
@@ -3747,28 +3747,28 @@
         <v>11.95</v>
       </c>
       <c r="M30">
-        <v>1.877694</v>
+        <v>1.9447545</v>
       </c>
       <c r="N30">
-        <v>10.072306</v>
+        <v>10.0052455</v>
       </c>
       <c r="O30">
-        <v>1.0072306</v>
+        <v>1.00052455</v>
       </c>
       <c r="P30">
-        <v>9.0650754</v>
+        <v>9.004720949999999</v>
       </c>
       <c r="Q30">
-        <v>12.8150754</v>
+        <v>12.75472095</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1135842982527354</v>
+        <v>0.1144682875361565</v>
       </c>
       <c r="T30">
-        <v>1.048601535979681</v>
+        <v>1.062276569051925</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.364189266195662</v>
+        <v>6.144734463913053</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09544478415067113</v>
+        <v>0.0956952735593728</v>
       </c>
       <c r="C31">
-        <v>96.20881534713152</v>
+        <v>94.62432572855867</v>
       </c>
       <c r="D31">
-        <v>126.6838153471315</v>
+        <v>126.3343257285587</v>
       </c>
       <c r="E31">
-        <v>-11.88500000000001</v>
+        <v>-10.65000000000001</v>
       </c>
       <c r="F31">
-        <v>35.815</v>
+        <v>37.05</v>
       </c>
       <c r="G31">
         <v>5.34</v>
@@ -3829,45 +3829,45 @@
         <v>11.95</v>
       </c>
       <c r="M31">
-        <v>1.9447545</v>
+        <v>2.048865</v>
       </c>
       <c r="N31">
-        <v>10.0052455</v>
+        <v>9.901135</v>
       </c>
       <c r="O31">
-        <v>1.00052455</v>
+        <v>0.9901135000000001</v>
       </c>
       <c r="P31">
-        <v>9.004720949999999</v>
+        <v>8.9110215</v>
       </c>
       <c r="Q31">
-        <v>12.75472095</v>
+        <v>12.6610215</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1144682875361565</v>
+        <v>0.1153775336562469</v>
       </c>
       <c r="T31">
-        <v>1.062276569051924</v>
+        <v>1.076342317354804</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.1</v>
       </c>
       <c r="W31">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.144734463913054</v>
+        <v>5.832497504716026</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0956952735593728</v>
+        <v>0.09568476296807449</v>
       </c>
       <c r="C32">
-        <v>94.62432572855867</v>
+        <v>93.40395162753438</v>
       </c>
       <c r="D32">
-        <v>126.3343257285587</v>
+        <v>126.3489516275344</v>
       </c>
       <c r="E32">
-        <v>-10.65000000000001</v>
+        <v>-9.415000000000006</v>
       </c>
       <c r="F32">
-        <v>37.05</v>
+        <v>38.285</v>
       </c>
       <c r="G32">
         <v>5.34</v>
@@ -3911,28 +3911,28 @@
         <v>11.95</v>
       </c>
       <c r="M32">
-        <v>2.048865</v>
+        <v>2.1171605</v>
       </c>
       <c r="N32">
-        <v>9.901135</v>
+        <v>9.832839499999999</v>
       </c>
       <c r="O32">
-        <v>0.9901135000000001</v>
+        <v>0.9832839499999999</v>
       </c>
       <c r="P32">
-        <v>8.9110215</v>
+        <v>8.849555549999998</v>
       </c>
       <c r="Q32">
-        <v>12.6610215</v>
+        <v>12.59955555</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1153775336562469</v>
+        <v>0.1163131347363398</v>
       </c>
       <c r="T32">
-        <v>1.076342317354804</v>
+        <v>1.090815768507043</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.832497504716026</v>
+        <v>5.644352423918734</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09568476296807449</v>
+        <v>0.09567425237677618</v>
       </c>
       <c r="C33">
-        <v>93.40395162753438</v>
+        <v>92.1835809134231</v>
       </c>
       <c r="D33">
-        <v>126.3489516275344</v>
+        <v>126.3635809134231</v>
       </c>
       <c r="E33">
-        <v>-9.415000000000006</v>
+        <v>-8.18</v>
       </c>
       <c r="F33">
-        <v>38.285</v>
+        <v>39.52</v>
       </c>
       <c r="G33">
         <v>5.34</v>
@@ -3993,28 +3993,28 @@
         <v>11.95</v>
       </c>
       <c r="M33">
-        <v>2.1171605</v>
+        <v>2.185456</v>
       </c>
       <c r="N33">
-        <v>9.832839499999999</v>
+        <v>9.764543999999999</v>
       </c>
       <c r="O33">
-        <v>0.9832839499999999</v>
+        <v>0.9764543999999999</v>
       </c>
       <c r="P33">
-        <v>8.849555549999998</v>
+        <v>8.788089599999999</v>
       </c>
       <c r="Q33">
-        <v>12.59955555</v>
+        <v>12.5380896</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1163131347363398</v>
+        <v>0.1172762534952591</v>
       </c>
       <c r="T33">
-        <v>1.090815768507043</v>
+        <v>1.105714909399053</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.644352423918734</v>
+        <v>5.467966410671273</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09567425237677618</v>
+        <v>0.09566374178547783</v>
       </c>
       <c r="C34">
-        <v>92.1835809134231</v>
+        <v>90.96321358740161</v>
       </c>
       <c r="D34">
-        <v>126.3635809134231</v>
+        <v>126.3782135874016</v>
       </c>
       <c r="E34">
-        <v>-8.18</v>
+        <v>-6.945</v>
       </c>
       <c r="F34">
-        <v>39.52</v>
+        <v>40.755</v>
       </c>
       <c r="G34">
         <v>5.34</v>
@@ -4075,28 +4075,28 @@
         <v>11.95</v>
       </c>
       <c r="M34">
-        <v>2.185456</v>
+        <v>2.2537515</v>
       </c>
       <c r="N34">
-        <v>9.764543999999999</v>
+        <v>9.696248499999999</v>
       </c>
       <c r="O34">
-        <v>0.9764543999999999</v>
+        <v>0.96962485</v>
       </c>
       <c r="P34">
-        <v>8.788089599999999</v>
+        <v>8.726623649999999</v>
       </c>
       <c r="Q34">
-        <v>12.5380896</v>
+        <v>12.47662365</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1172762534952591</v>
+        <v>0.1182681220678774</v>
       </c>
       <c r="T34">
-        <v>1.105714909399053</v>
+        <v>1.121058800765452</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.467966410671273</v>
+        <v>5.30227045883275</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09566374178547783</v>
+        <v>0.09565323119417952</v>
       </c>
       <c r="C35">
-        <v>90.96321358740161</v>
+        <v>89.7428496506468</v>
       </c>
       <c r="D35">
-        <v>126.3782135874016</v>
+        <v>126.3928496506468</v>
       </c>
       <c r="E35">
-        <v>-6.945</v>
+        <v>-5.710000000000001</v>
       </c>
       <c r="F35">
-        <v>40.755</v>
+        <v>41.99</v>
       </c>
       <c r="G35">
         <v>5.34</v>
@@ -4157,28 +4157,28 @@
         <v>11.95</v>
       </c>
       <c r="M35">
-        <v>2.2537515</v>
+        <v>2.322047</v>
       </c>
       <c r="N35">
-        <v>9.696248499999999</v>
+        <v>9.627953</v>
       </c>
       <c r="O35">
-        <v>0.96962485</v>
+        <v>0.9627953</v>
       </c>
       <c r="P35">
-        <v>8.726623649999999</v>
+        <v>8.6651577</v>
       </c>
       <c r="Q35">
-        <v>12.47662365</v>
+        <v>12.4151577</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1182681220678774</v>
+        <v>0.1192900472639084</v>
       </c>
       <c r="T35">
-        <v>1.121058800765452</v>
+        <v>1.136867658536893</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.30227045883275</v>
+        <v>5.146321327690611</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09565323119417952</v>
+        <v>0.09564272060288119</v>
       </c>
       <c r="C36">
-        <v>89.7428496506468</v>
+        <v>88.52248910433659</v>
       </c>
       <c r="D36">
-        <v>126.3928496506468</v>
+        <v>126.4074891043366</v>
       </c>
       <c r="E36">
-        <v>-5.710000000000001</v>
+        <v>-4.475000000000001</v>
       </c>
       <c r="F36">
-        <v>41.99</v>
+        <v>43.225</v>
       </c>
       <c r="G36">
         <v>5.34</v>
@@ -4239,28 +4239,28 @@
         <v>11.95</v>
       </c>
       <c r="M36">
-        <v>2.322047</v>
+        <v>2.3903425</v>
       </c>
       <c r="N36">
-        <v>9.627953</v>
+        <v>9.5596575</v>
       </c>
       <c r="O36">
-        <v>0.9627953</v>
+        <v>0.9559657500000001</v>
       </c>
       <c r="P36">
-        <v>8.6651577</v>
+        <v>8.603691749999999</v>
       </c>
       <c r="Q36">
-        <v>12.4151577</v>
+        <v>12.35369175</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1192900472639084</v>
+        <v>0.1203434163121249</v>
       </c>
       <c r="T36">
-        <v>1.136867658536893</v>
+        <v>1.153162942701301</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.146321327690611</v>
+        <v>4.999283575470879</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09564272060288119</v>
+        <v>0.09563221001158287</v>
       </c>
       <c r="C37">
-        <v>88.52248910433659</v>
+        <v>87.30213194964898</v>
       </c>
       <c r="D37">
-        <v>126.4074891043366</v>
+        <v>126.422131949649</v>
       </c>
       <c r="E37">
-        <v>-4.475000000000001</v>
+        <v>-3.239999999999995</v>
       </c>
       <c r="F37">
-        <v>43.225</v>
+        <v>44.46000000000001</v>
       </c>
       <c r="G37">
         <v>5.34</v>
@@ -4321,28 +4321,28 @@
         <v>11.95</v>
       </c>
       <c r="M37">
-        <v>2.3903425</v>
+        <v>2.458638000000001</v>
       </c>
       <c r="N37">
-        <v>9.5596575</v>
+        <v>9.491361999999999</v>
       </c>
       <c r="O37">
-        <v>0.9559657500000001</v>
+        <v>0.9491361999999999</v>
       </c>
       <c r="P37">
-        <v>8.603691749999999</v>
+        <v>8.542225799999999</v>
       </c>
       <c r="Q37">
-        <v>12.35369175</v>
+        <v>12.2922258</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1203434163121249</v>
+        <v>0.1214297031430983</v>
       </c>
       <c r="T37">
-        <v>1.153162942701301</v>
+        <v>1.169967454495847</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.999283575470879</v>
+        <v>4.860414587263353</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0956322100115829</v>
+        <v>0.09562169942028456</v>
       </c>
       <c r="C38">
-        <v>87.30213194964895</v>
+        <v>86.08177818776292</v>
       </c>
       <c r="D38">
-        <v>126.422131949649</v>
+        <v>126.4367781877629</v>
       </c>
       <c r="E38">
-        <v>-3.240000000000002</v>
+        <v>-2.005000000000003</v>
       </c>
       <c r="F38">
-        <v>44.46</v>
+        <v>45.695</v>
       </c>
       <c r="G38">
         <v>5.34</v>
@@ -4403,28 +4403,28 @@
         <v>11.95</v>
       </c>
       <c r="M38">
-        <v>2.458638</v>
+        <v>2.5269335</v>
       </c>
       <c r="N38">
-        <v>9.491361999999999</v>
+        <v>9.423066499999999</v>
       </c>
       <c r="O38">
-        <v>0.9491361999999999</v>
+        <v>0.9423066499999999</v>
       </c>
       <c r="P38">
-        <v>8.542225799999999</v>
+        <v>8.480759849999998</v>
       </c>
       <c r="Q38">
-        <v>12.2922258</v>
+        <v>12.23075985</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1214297031430983</v>
+        <v>0.1225504752702929</v>
       </c>
       <c r="T38">
-        <v>1.169967454495847</v>
+        <v>1.187305442855299</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.860414587263354</v>
+        <v>4.729052030850831</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09562169942028456</v>
+        <v>0.09561118882898624</v>
       </c>
       <c r="C39">
-        <v>86.08177818776292</v>
+        <v>84.86142781985765</v>
       </c>
       <c r="D39">
-        <v>126.4367781877629</v>
+        <v>126.4514278198577</v>
       </c>
       <c r="E39">
-        <v>-2.005000000000003</v>
+        <v>-0.7700000000000031</v>
       </c>
       <c r="F39">
-        <v>45.695</v>
+        <v>46.93</v>
       </c>
       <c r="G39">
         <v>5.34</v>
@@ -4485,28 +4485,28 @@
         <v>11.95</v>
       </c>
       <c r="M39">
-        <v>2.5269335</v>
+        <v>2.595229</v>
       </c>
       <c r="N39">
-        <v>9.423066499999999</v>
+        <v>9.354771</v>
       </c>
       <c r="O39">
-        <v>0.9423066499999999</v>
+        <v>0.9354771</v>
       </c>
       <c r="P39">
-        <v>8.480759849999998</v>
+        <v>8.4192939</v>
       </c>
       <c r="Q39">
-        <v>12.23075985</v>
+        <v>12.1692939</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1225504752702929</v>
+        <v>0.1237074013370746</v>
       </c>
       <c r="T39">
-        <v>1.187305442855299</v>
+        <v>1.205202721161831</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.729052030850831</v>
+        <v>4.604603293196861</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09561118882898624</v>
+        <v>0.09647817823768792</v>
       </c>
       <c r="C40">
-        <v>84.86142781985765</v>
+        <v>82.42932167580867</v>
       </c>
       <c r="D40">
-        <v>126.4514278198577</v>
+        <v>125.2543216758087</v>
       </c>
       <c r="E40">
-        <v>-0.7700000000000031</v>
+        <v>0.4649999999999963</v>
       </c>
       <c r="F40">
-        <v>46.93</v>
+        <v>48.165</v>
       </c>
       <c r="G40">
         <v>5.34</v>
@@ -4567,45 +4567,45 @@
         <v>11.95</v>
       </c>
       <c r="M40">
-        <v>2.595229</v>
+        <v>2.783937</v>
       </c>
       <c r="N40">
-        <v>9.354771</v>
+        <v>9.166062999999999</v>
       </c>
       <c r="O40">
-        <v>0.9354771</v>
+        <v>0.9166063</v>
       </c>
       <c r="P40">
-        <v>8.4192939</v>
+        <v>8.2494567</v>
       </c>
       <c r="Q40">
-        <v>12.1692939</v>
+        <v>11.9994567</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1237074013370746</v>
+        <v>0.1249022594060458</v>
       </c>
       <c r="T40">
-        <v>1.205202721161831</v>
+        <v>1.223686795478413</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.1</v>
       </c>
       <c r="W40">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.604603293196861</v>
+        <v>4.292482193382968</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09647817823768792</v>
+        <v>0.0964901676463896</v>
       </c>
       <c r="C41">
-        <v>82.42932167580867</v>
+        <v>81.17792602115568</v>
       </c>
       <c r="D41">
-        <v>125.2543216758087</v>
+        <v>125.2379260211557</v>
       </c>
       <c r="E41">
-        <v>0.4649999999999963</v>
+        <v>1.700000000000003</v>
       </c>
       <c r="F41">
-        <v>48.165</v>
+        <v>49.40000000000001</v>
       </c>
       <c r="G41">
         <v>5.34</v>
@@ -4649,28 +4649,28 @@
         <v>11.95</v>
       </c>
       <c r="M41">
-        <v>2.783937</v>
+        <v>2.855320000000001</v>
       </c>
       <c r="N41">
-        <v>9.166062999999999</v>
+        <v>9.094679999999999</v>
       </c>
       <c r="O41">
-        <v>0.9166063</v>
+        <v>0.9094679999999999</v>
       </c>
       <c r="P41">
-        <v>8.2494567</v>
+        <v>8.185211999999998</v>
       </c>
       <c r="Q41">
-        <v>11.9994567</v>
+        <v>11.935212</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1249022594060458</v>
+        <v>0.126136946077316</v>
       </c>
       <c r="T41">
-        <v>1.223686795478413</v>
+        <v>1.242787005605547</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.292482193382968</v>
+        <v>4.185170138548393</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0964901676463896</v>
+        <v>0.09650215705509127</v>
       </c>
       <c r="C42">
-        <v>81.17792602115568</v>
+        <v>79.92653465828771</v>
       </c>
       <c r="D42">
-        <v>125.2379260211557</v>
+        <v>125.2215346582877</v>
       </c>
       <c r="E42">
-        <v>1.700000000000003</v>
+        <v>2.935000000000002</v>
       </c>
       <c r="F42">
-        <v>49.40000000000001</v>
+        <v>50.63500000000001</v>
       </c>
       <c r="G42">
         <v>5.34</v>
@@ -4731,28 +4731,28 @@
         <v>11.95</v>
       </c>
       <c r="M42">
-        <v>2.855320000000001</v>
+        <v>2.926703000000001</v>
       </c>
       <c r="N42">
-        <v>9.094679999999999</v>
+        <v>9.023296999999999</v>
       </c>
       <c r="O42">
-        <v>0.9094679999999999</v>
+        <v>0.9023297</v>
       </c>
       <c r="P42">
-        <v>8.185211999999998</v>
+        <v>8.1209673</v>
       </c>
       <c r="Q42">
-        <v>11.935212</v>
+        <v>11.8709673</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.126136946077316</v>
+        <v>0.127413486534053</v>
       </c>
       <c r="T42">
-        <v>1.242787005605547</v>
+        <v>1.262534680482754</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.185170138548393</v>
+        <v>4.083092818095993</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09650215705509127</v>
+        <v>0.09783714646379295</v>
       </c>
       <c r="C43">
-        <v>79.92653465828771</v>
+        <v>76.89285084397349</v>
       </c>
       <c r="D43">
-        <v>125.2215346582877</v>
+        <v>123.4228508439735</v>
       </c>
       <c r="E43">
-        <v>2.935000000000002</v>
+        <v>4.170000000000002</v>
       </c>
       <c r="F43">
-        <v>50.63500000000001</v>
+        <v>51.87</v>
       </c>
       <c r="G43">
         <v>5.34</v>
@@ -4813,45 +4813,45 @@
         <v>11.95</v>
       </c>
       <c r="M43">
-        <v>2.926703000000001</v>
+        <v>3.179631</v>
       </c>
       <c r="N43">
-        <v>9.023296999999999</v>
+        <v>8.770368999999999</v>
       </c>
       <c r="O43">
-        <v>0.9023297</v>
+        <v>0.8770368999999999</v>
       </c>
       <c r="P43">
-        <v>8.1209673</v>
+        <v>7.893332099999999</v>
       </c>
       <c r="Q43">
-        <v>11.8709673</v>
+        <v>11.6433321</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.127413486534053</v>
+        <v>0.1287340456272292</v>
       </c>
       <c r="T43">
-        <v>1.262534680482754</v>
+        <v>1.282963309666071</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.1</v>
       </c>
       <c r="W43">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.083092818095993</v>
+        <v>3.758297739580473</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09783714646379296</v>
+        <v>0.09788063587249463</v>
       </c>
       <c r="C44">
-        <v>76.89285084397346</v>
+        <v>75.60012452181363</v>
       </c>
       <c r="D44">
-        <v>123.4228508439735</v>
+        <v>123.3651245218136</v>
       </c>
       <c r="E44">
-        <v>4.169999999999995</v>
+        <v>5.404999999999994</v>
       </c>
       <c r="F44">
-        <v>51.87</v>
+        <v>53.105</v>
       </c>
       <c r="G44">
         <v>5.34</v>
@@ -4895,28 +4895,28 @@
         <v>11.95</v>
       </c>
       <c r="M44">
-        <v>3.179631</v>
+        <v>3.2553365</v>
       </c>
       <c r="N44">
-        <v>8.770368999999999</v>
+        <v>8.694663499999999</v>
       </c>
       <c r="O44">
-        <v>0.8770368999999999</v>
+        <v>0.8694663499999999</v>
       </c>
       <c r="P44">
-        <v>7.893332099999999</v>
+        <v>7.825197149999999</v>
       </c>
       <c r="Q44">
-        <v>11.6433321</v>
+        <v>11.57519715</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1287340456272292</v>
+        <v>0.1301009401271835</v>
       </c>
       <c r="T44">
-        <v>1.282963309666071</v>
+        <v>1.304108732855821</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.758297739580473</v>
+        <v>3.670895466566974</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09788063587249463</v>
+        <v>0.0979241252811963</v>
       </c>
       <c r="C45">
-        <v>75.60012452181363</v>
+        <v>74.30745217297246</v>
       </c>
       <c r="D45">
-        <v>123.3651245218136</v>
+        <v>123.3074521729725</v>
       </c>
       <c r="E45">
-        <v>5.404999999999994</v>
+        <v>6.640000000000001</v>
       </c>
       <c r="F45">
-        <v>53.105</v>
+        <v>54.34</v>
       </c>
       <c r="G45">
         <v>5.34</v>
@@ -4977,28 +4977,28 @@
         <v>11.95</v>
       </c>
       <c r="M45">
-        <v>3.2553365</v>
+        <v>3.331042</v>
       </c>
       <c r="N45">
-        <v>8.694663499999999</v>
+        <v>8.618957999999999</v>
       </c>
       <c r="O45">
-        <v>0.8694663499999999</v>
+        <v>0.8618958</v>
       </c>
       <c r="P45">
-        <v>7.825197149999999</v>
+        <v>7.757062199999999</v>
       </c>
       <c r="Q45">
-        <v>11.57519715</v>
+        <v>11.5070622</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1301009401271835</v>
+        <v>0.1315166522878505</v>
       </c>
       <c r="T45">
-        <v>1.304108732855821</v>
+        <v>1.326009349730919</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.670895466566974</v>
+        <v>3.587466024144997</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0979241252811963</v>
+        <v>0.09796761468989798</v>
       </c>
       <c r="C46">
-        <v>74.30745217297246</v>
+        <v>73.01483372178886</v>
       </c>
       <c r="D46">
-        <v>123.3074521729725</v>
+        <v>123.2498337217889</v>
       </c>
       <c r="E46">
-        <v>6.640000000000001</v>
+        <v>7.875</v>
       </c>
       <c r="F46">
-        <v>54.34</v>
+        <v>55.575</v>
       </c>
       <c r="G46">
         <v>5.34</v>
@@ -5059,28 +5059,28 @@
         <v>11.95</v>
       </c>
       <c r="M46">
-        <v>3.331042</v>
+        <v>3.4067475</v>
       </c>
       <c r="N46">
-        <v>8.618957999999999</v>
+        <v>8.543252499999999</v>
       </c>
       <c r="O46">
-        <v>0.8618958</v>
+        <v>0.85432525</v>
       </c>
       <c r="P46">
-        <v>7.757062199999999</v>
+        <v>7.688927249999999</v>
       </c>
       <c r="Q46">
-        <v>11.5070622</v>
+        <v>11.43892725</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1315166522878505</v>
+        <v>0.1329838448907236</v>
       </c>
       <c r="T46">
-        <v>1.326009349730919</v>
+        <v>1.348706352674202</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.587466024144997</v>
+        <v>3.507744556941775</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09796761468989798</v>
+        <v>0.09917030409859967</v>
       </c>
       <c r="C47">
-        <v>73.01483372178886</v>
+        <v>70.20747216155362</v>
       </c>
       <c r="D47">
-        <v>123.2498337217889</v>
+        <v>121.6774721615536</v>
       </c>
       <c r="E47">
-        <v>7.875</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F47">
-        <v>55.575</v>
+        <v>56.81</v>
       </c>
       <c r="G47">
         <v>5.34</v>
@@ -5141,45 +5141,45 @@
         <v>11.95</v>
       </c>
       <c r="M47">
-        <v>3.4067475</v>
+        <v>3.641521</v>
       </c>
       <c r="N47">
-        <v>8.543252499999999</v>
+        <v>8.308478999999998</v>
       </c>
       <c r="O47">
-        <v>0.85432525</v>
+        <v>0.8308478999999999</v>
       </c>
       <c r="P47">
-        <v>7.688927249999999</v>
+        <v>7.477631099999998</v>
       </c>
       <c r="Q47">
-        <v>11.43892725</v>
+        <v>11.2276311</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1329838448907236</v>
+        <v>0.1345053779603697</v>
       </c>
       <c r="T47">
-        <v>1.348706352674202</v>
+        <v>1.372243985356125</v>
       </c>
       <c r="U47">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0.1</v>
       </c>
       <c r="W47">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.507744556941775</v>
+        <v>3.281595794724237</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09917030409859967</v>
+        <v>0.09923899350730135</v>
       </c>
       <c r="C48">
-        <v>70.20747216155362</v>
+        <v>68.88387981097718</v>
       </c>
       <c r="D48">
-        <v>121.6774721615536</v>
+        <v>121.5888798109772</v>
       </c>
       <c r="E48">
-        <v>9.109999999999999</v>
+        <v>10.345</v>
       </c>
       <c r="F48">
-        <v>56.81</v>
+        <v>58.045</v>
       </c>
       <c r="G48">
         <v>5.34</v>
@@ -5223,28 +5223,28 @@
         <v>11.95</v>
       </c>
       <c r="M48">
-        <v>3.641521</v>
+        <v>3.7206845</v>
       </c>
       <c r="N48">
-        <v>8.308478999999998</v>
+        <v>8.229315499999998</v>
       </c>
       <c r="O48">
-        <v>0.8308478999999999</v>
+        <v>0.8229315499999998</v>
       </c>
       <c r="P48">
-        <v>7.477631099999998</v>
+        <v>7.406383949999999</v>
       </c>
       <c r="Q48">
-        <v>11.2276311</v>
+        <v>11.15638395</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1345053779603697</v>
+        <v>0.1360843273722667</v>
       </c>
       <c r="T48">
-        <v>1.372243985356125</v>
+        <v>1.396669830592083</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.281595794724237</v>
+        <v>3.211774607602444</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09923899350730135</v>
+        <v>0.09930768291600303</v>
       </c>
       <c r="C49">
-        <v>68.88387981097718</v>
+        <v>67.56041637324049</v>
       </c>
       <c r="D49">
-        <v>121.5888798109772</v>
+        <v>121.5004163732405</v>
       </c>
       <c r="E49">
-        <v>10.345</v>
+        <v>11.58</v>
       </c>
       <c r="F49">
-        <v>58.045</v>
+        <v>59.28</v>
       </c>
       <c r="G49">
         <v>5.34</v>
@@ -5305,28 +5305,28 @@
         <v>11.95</v>
       </c>
       <c r="M49">
-        <v>3.7206845</v>
+        <v>3.799848</v>
       </c>
       <c r="N49">
-        <v>8.229315499999998</v>
+        <v>8.150151999999999</v>
       </c>
       <c r="O49">
-        <v>0.8229315499999998</v>
+        <v>0.8150151999999999</v>
       </c>
       <c r="P49">
-        <v>7.406383949999999</v>
+        <v>7.335136799999999</v>
       </c>
       <c r="Q49">
-        <v>11.15638395</v>
+        <v>11.0851368</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1360843273722667</v>
+        <v>0.1377240056076981</v>
       </c>
       <c r="T49">
-        <v>1.396669830592083</v>
+        <v>1.42203513141404</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.211774607602444</v>
+        <v>3.144862636610727</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09930768291600302</v>
+        <v>0.0993763723247047</v>
       </c>
       <c r="C50">
-        <v>67.56041637324049</v>
+        <v>66.23708156717187</v>
       </c>
       <c r="D50">
-        <v>121.5004163732405</v>
+        <v>121.4120815671719</v>
       </c>
       <c r="E50">
-        <v>11.58</v>
+        <v>12.815</v>
       </c>
       <c r="F50">
-        <v>59.28</v>
+        <v>60.515</v>
       </c>
       <c r="G50">
         <v>5.34</v>
@@ -5387,28 +5387,28 @@
         <v>11.95</v>
       </c>
       <c r="M50">
-        <v>3.799848</v>
+        <v>3.8790115</v>
       </c>
       <c r="N50">
-        <v>8.150151999999999</v>
+        <v>8.070988499999999</v>
       </c>
       <c r="O50">
-        <v>0.8150151999999999</v>
+        <v>0.8070988499999999</v>
       </c>
       <c r="P50">
-        <v>7.335136799999999</v>
+        <v>7.263889649999999</v>
       </c>
       <c r="Q50">
-        <v>11.0851368</v>
+        <v>11.01388965</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1377240056076981</v>
+        <v>0.1394279849504013</v>
       </c>
       <c r="T50">
-        <v>1.42203513141404</v>
+        <v>1.448395149915289</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.144862636610727</v>
+        <v>3.080681766475814</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0993763723247047</v>
+        <v>0.09944506173340636</v>
       </c>
       <c r="C51">
-        <v>66.23708156717187</v>
+        <v>64.91387511241683</v>
       </c>
       <c r="D51">
-        <v>121.4120815671719</v>
+        <v>121.3238751124168</v>
       </c>
       <c r="E51">
-        <v>12.815</v>
+        <v>14.05</v>
       </c>
       <c r="F51">
-        <v>60.515</v>
+        <v>61.75</v>
       </c>
       <c r="G51">
         <v>5.34</v>
@@ -5469,28 +5469,28 @@
         <v>11.95</v>
       </c>
       <c r="M51">
-        <v>3.8790115</v>
+        <v>3.958175</v>
       </c>
       <c r="N51">
-        <v>8.070988499999999</v>
+        <v>7.991824999999999</v>
       </c>
       <c r="O51">
-        <v>0.8070988499999999</v>
+        <v>0.7991824999999999</v>
       </c>
       <c r="P51">
-        <v>7.263889649999999</v>
+        <v>7.192642499999999</v>
       </c>
       <c r="Q51">
-        <v>11.01388965</v>
+        <v>10.9426425</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1394279849504013</v>
+        <v>0.1412001234668127</v>
       </c>
       <c r="T51">
-        <v>1.448395149915289</v>
+        <v>1.475809569156587</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.080681766475814</v>
+        <v>3.019068131146298</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09944506173340636</v>
+        <v>0.103093951142108</v>
       </c>
       <c r="C52">
-        <v>64.91387511241683</v>
+        <v>59.17060181405486</v>
       </c>
       <c r="D52">
-        <v>121.3238751124168</v>
+        <v>116.8156018140549</v>
       </c>
       <c r="E52">
-        <v>14.05</v>
+        <v>15.285</v>
       </c>
       <c r="F52">
-        <v>61.75</v>
+        <v>62.985</v>
       </c>
       <c r="G52">
         <v>5.34</v>
@@ -5551,45 +5551,45 @@
         <v>11.95</v>
       </c>
       <c r="M52">
-        <v>3.958175</v>
+        <v>4.528621500000001</v>
       </c>
       <c r="N52">
-        <v>7.991824999999999</v>
+        <v>7.421378499999999</v>
       </c>
       <c r="O52">
-        <v>0.7991824999999999</v>
+        <v>0.7421378499999999</v>
       </c>
       <c r="P52">
-        <v>7.192642499999999</v>
+        <v>6.679240649999999</v>
       </c>
       <c r="Q52">
-        <v>10.9426425</v>
+        <v>10.42924065</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1412001234668127</v>
+        <v>0.1430445941675674</v>
       </c>
       <c r="T52">
-        <v>1.475809569156587</v>
+        <v>1.504342944285286</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.1</v>
       </c>
       <c r="W52">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.019068131146298</v>
+        <v>2.638772085501073</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.103093951142108</v>
+        <v>0.1032328405508097</v>
       </c>
       <c r="C53">
-        <v>59.17060181405486</v>
+        <v>57.77061113538812</v>
       </c>
       <c r="D53">
-        <v>116.8156018140549</v>
+        <v>116.6506111353881</v>
       </c>
       <c r="E53">
-        <v>15.285</v>
+        <v>16.52</v>
       </c>
       <c r="F53">
-        <v>62.985</v>
+        <v>64.22</v>
       </c>
       <c r="G53">
         <v>5.34</v>
@@ -5633,28 +5633,28 @@
         <v>11.95</v>
       </c>
       <c r="M53">
-        <v>4.528621500000001</v>
+        <v>4.617418000000001</v>
       </c>
       <c r="N53">
-        <v>7.421378499999999</v>
+        <v>7.332581999999999</v>
       </c>
       <c r="O53">
-        <v>0.7421378499999999</v>
+        <v>0.7332581999999999</v>
       </c>
       <c r="P53">
-        <v>6.679240649999999</v>
+        <v>6.599323799999999</v>
       </c>
       <c r="Q53">
-        <v>10.42924065</v>
+        <v>10.3493238</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1430445941675674</v>
+        <v>0.1449659178141869</v>
       </c>
       <c r="T53">
-        <v>1.504342944285286</v>
+        <v>1.534065210044347</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.638772085501073</v>
+        <v>2.588026468472206</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1032328405508097</v>
+        <v>0.1033717299595114</v>
       </c>
       <c r="C54">
-        <v>57.77061113538812</v>
+        <v>56.37108586595664</v>
       </c>
       <c r="D54">
-        <v>116.6506111353881</v>
+        <v>116.4860858659566</v>
       </c>
       <c r="E54">
-        <v>16.52</v>
+        <v>17.755</v>
       </c>
       <c r="F54">
-        <v>64.22</v>
+        <v>65.455</v>
       </c>
       <c r="G54">
         <v>5.34</v>
@@ -5715,28 +5715,28 @@
         <v>11.95</v>
       </c>
       <c r="M54">
-        <v>4.617418000000001</v>
+        <v>4.706214500000001</v>
       </c>
       <c r="N54">
-        <v>7.332581999999999</v>
+        <v>7.243785499999999</v>
       </c>
       <c r="O54">
-        <v>0.7332581999999999</v>
+        <v>0.72437855</v>
       </c>
       <c r="P54">
-        <v>6.599323799999999</v>
+        <v>6.519406949999999</v>
       </c>
       <c r="Q54">
-        <v>10.3493238</v>
+        <v>10.26940695</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1449659178141869</v>
+        <v>0.146968999913854</v>
       </c>
       <c r="T54">
-        <v>1.534065210044347</v>
+        <v>1.565052253069751</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.588026468472206</v>
+        <v>2.539195780387825</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1033717299595114</v>
+        <v>0.1054060193682131</v>
       </c>
       <c r="C55">
-        <v>56.37108586595664</v>
+        <v>52.77841600908718</v>
       </c>
       <c r="D55">
-        <v>116.4860858659566</v>
+        <v>114.1284160090872</v>
       </c>
       <c r="E55">
-        <v>17.755</v>
+        <v>18.98999999999999</v>
       </c>
       <c r="F55">
-        <v>65.455</v>
+        <v>66.69</v>
       </c>
       <c r="G55">
         <v>5.34</v>
@@ -5797,45 +5797,45 @@
         <v>11.95</v>
       </c>
       <c r="M55">
-        <v>4.706214500000001</v>
+        <v>5.055102000000001</v>
       </c>
       <c r="N55">
-        <v>7.243785499999999</v>
+        <v>6.894897999999999</v>
       </c>
       <c r="O55">
-        <v>0.72437855</v>
+        <v>0.6894897999999999</v>
       </c>
       <c r="P55">
-        <v>6.519406949999999</v>
+        <v>6.205408199999999</v>
       </c>
       <c r="Q55">
-        <v>10.26940695</v>
+        <v>9.955408199999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.146968999913854</v>
+        <v>0.1490591725395937</v>
       </c>
       <c r="T55">
-        <v>1.565052253069751</v>
+        <v>1.597386558835391</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.1</v>
       </c>
       <c r="W55">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.539195780387825</v>
+        <v>2.363948343673381</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1054060193682131</v>
+        <v>0.1055800087769148</v>
       </c>
       <c r="C56">
-        <v>52.77841600908718</v>
+        <v>51.34619115170449</v>
       </c>
       <c r="D56">
-        <v>114.1284160090872</v>
+        <v>113.9311911517045</v>
       </c>
       <c r="E56">
-        <v>18.98999999999999</v>
+        <v>20.22500000000001</v>
       </c>
       <c r="F56">
-        <v>66.69</v>
+        <v>67.92500000000001</v>
       </c>
       <c r="G56">
         <v>5.34</v>
@@ -5879,28 +5879,28 @@
         <v>11.95</v>
       </c>
       <c r="M56">
-        <v>5.055102000000001</v>
+        <v>5.148715000000001</v>
       </c>
       <c r="N56">
-        <v>6.894897999999999</v>
+        <v>6.801284999999998</v>
       </c>
       <c r="O56">
-        <v>0.6894897999999999</v>
+        <v>0.6801284999999999</v>
       </c>
       <c r="P56">
-        <v>6.205408199999999</v>
+        <v>6.121156499999998</v>
       </c>
       <c r="Q56">
-        <v>9.955408199999999</v>
+        <v>9.871156499999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1490591725395937</v>
+        <v>0.1512422417264772</v>
       </c>
       <c r="T56">
-        <v>1.597386558835391</v>
+        <v>1.631157944857281</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.363948343673381</v>
+        <v>2.320967464697501</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1055800087769148</v>
+        <v>0.1057539981856164</v>
       </c>
       <c r="C57">
-        <v>51.34619115170449</v>
+        <v>49.91464676537053</v>
       </c>
       <c r="D57">
-        <v>113.9311911517045</v>
+        <v>113.7346467653705</v>
       </c>
       <c r="E57">
-        <v>20.22500000000001</v>
+        <v>21.46000000000001</v>
       </c>
       <c r="F57">
-        <v>67.92500000000001</v>
+        <v>69.16000000000001</v>
       </c>
       <c r="G57">
         <v>5.34</v>
@@ -5961,28 +5961,28 @@
         <v>11.95</v>
       </c>
       <c r="M57">
-        <v>5.148715000000001</v>
+        <v>5.242328000000001</v>
       </c>
       <c r="N57">
-        <v>6.801284999999998</v>
+        <v>6.707671999999998</v>
       </c>
       <c r="O57">
-        <v>0.6801284999999999</v>
+        <v>0.6707671999999998</v>
       </c>
       <c r="P57">
-        <v>6.121156499999998</v>
+        <v>6.036904799999999</v>
       </c>
       <c r="Q57">
-        <v>9.871156499999998</v>
+        <v>9.786904799999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1512422417264772</v>
+        <v>0.1535245413309464</v>
       </c>
       <c r="T57">
-        <v>1.631157944857281</v>
+        <v>1.666464393880166</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.320967464697501</v>
+        <v>2.279521617113617</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1057539981856164</v>
+        <v>0.1059279875943181</v>
       </c>
       <c r="C58">
-        <v>49.91464676537053</v>
+        <v>48.48377933447806</v>
       </c>
       <c r="D58">
-        <v>113.7346467653705</v>
+        <v>113.5387793344781</v>
       </c>
       <c r="E58">
-        <v>21.46000000000001</v>
+        <v>22.69500000000001</v>
       </c>
       <c r="F58">
-        <v>69.16000000000001</v>
+        <v>70.39500000000001</v>
       </c>
       <c r="G58">
         <v>5.34</v>
@@ -6043,28 +6043,28 @@
         <v>11.95</v>
       </c>
       <c r="M58">
-        <v>5.242328000000001</v>
+        <v>5.335941000000001</v>
       </c>
       <c r="N58">
-        <v>6.707671999999998</v>
+        <v>6.614058999999998</v>
       </c>
       <c r="O58">
-        <v>0.6707671999999998</v>
+        <v>0.6614058999999999</v>
       </c>
       <c r="P58">
-        <v>6.036904799999999</v>
+        <v>5.952653099999998</v>
       </c>
       <c r="Q58">
-        <v>9.786904799999999</v>
+        <v>9.702653099999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1535245413309464</v>
+        <v>0.155912994405391</v>
       </c>
       <c r="T58">
-        <v>1.666464393880166</v>
+        <v>1.70341300332272</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.279521617113617</v>
+        <v>2.239530009795835</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1059279875943181</v>
+        <v>0.1061019770030198</v>
       </c>
       <c r="C59">
-        <v>48.48377933447806</v>
+        <v>47.05358536759576</v>
       </c>
       <c r="D59">
-        <v>113.5387793344781</v>
+        <v>113.3435853675958</v>
       </c>
       <c r="E59">
-        <v>22.69500000000001</v>
+        <v>23.93000000000001</v>
       </c>
       <c r="F59">
-        <v>70.39500000000001</v>
+        <v>71.63000000000001</v>
       </c>
       <c r="G59">
         <v>5.34</v>
@@ -6125,28 +6125,28 @@
         <v>11.95</v>
       </c>
       <c r="M59">
-        <v>5.335941000000001</v>
+        <v>5.429554000000001</v>
       </c>
       <c r="N59">
-        <v>6.614058999999998</v>
+        <v>6.520445999999998</v>
       </c>
       <c r="O59">
-        <v>0.6614058999999999</v>
+        <v>0.6520445999999999</v>
       </c>
       <c r="P59">
-        <v>5.952653099999998</v>
+        <v>5.868401399999998</v>
       </c>
       <c r="Q59">
-        <v>9.702653099999999</v>
+        <v>9.618401399999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.155912994405391</v>
+        <v>0.1584151833405233</v>
       </c>
       <c r="T59">
-        <v>1.70341300332272</v>
+        <v>1.742121070357776</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.239530009795835</v>
+        <v>2.200917423420044</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1061019770030198</v>
+        <v>0.1062759664117215</v>
       </c>
       <c r="C60">
-        <v>47.05358536759577</v>
+        <v>45.62406139726069</v>
       </c>
       <c r="D60">
-        <v>113.3435853675958</v>
+        <v>113.1490613972607</v>
       </c>
       <c r="E60">
-        <v>23.92999999999999</v>
+        <v>25.16499999999999</v>
       </c>
       <c r="F60">
-        <v>71.63</v>
+        <v>72.86499999999999</v>
       </c>
       <c r="G60">
         <v>5.34</v>
@@ -6207,28 +6207,28 @@
         <v>11.95</v>
       </c>
       <c r="M60">
-        <v>5.429554</v>
+        <v>5.523167</v>
       </c>
       <c r="N60">
-        <v>6.520445999999999</v>
+        <v>6.426832999999999</v>
       </c>
       <c r="O60">
-        <v>0.6520446</v>
+        <v>0.6426833</v>
       </c>
       <c r="P60">
-        <v>5.868401399999999</v>
+        <v>5.7841497</v>
       </c>
       <c r="Q60">
-        <v>9.6184014</v>
+        <v>9.5341497</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1584151833405233</v>
+        <v>0.1610394302724914</v>
       </c>
       <c r="T60">
-        <v>1.742121070357776</v>
+        <v>1.782717335784786</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.200917423420045</v>
+        <v>2.163613738277332</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1062759664117215</v>
+        <v>0.1064499558204231</v>
       </c>
       <c r="C61">
-        <v>45.62406139726069</v>
+        <v>44.19520397977307</v>
       </c>
       <c r="D61">
-        <v>113.1490613972607</v>
+        <v>112.9552039797731</v>
       </c>
       <c r="E61">
-        <v>25.16499999999999</v>
+        <v>26.39999999999999</v>
       </c>
       <c r="F61">
-        <v>72.86499999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G61">
         <v>5.34</v>
@@ -6289,28 +6289,28 @@
         <v>11.95</v>
       </c>
       <c r="M61">
-        <v>5.523167</v>
+        <v>5.61678</v>
       </c>
       <c r="N61">
-        <v>6.426832999999999</v>
+        <v>6.333219999999999</v>
       </c>
       <c r="O61">
-        <v>0.6426833</v>
+        <v>0.6333219999999999</v>
       </c>
       <c r="P61">
-        <v>5.7841497</v>
+        <v>5.699897999999999</v>
       </c>
       <c r="Q61">
-        <v>9.5341497</v>
+        <v>9.449897999999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1610394302724914</v>
+        <v>0.1637948895510578</v>
       </c>
       <c r="T61">
-        <v>1.782717335784786</v>
+        <v>1.825343414483147</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.163613738277332</v>
+        <v>2.127553509306043</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1064499558204231</v>
+        <v>0.1066239452291248</v>
       </c>
       <c r="C62">
-        <v>44.19520397977307</v>
+        <v>42.76700969499288</v>
       </c>
       <c r="D62">
-        <v>112.9552039797731</v>
+        <v>112.7620096949929</v>
       </c>
       <c r="E62">
-        <v>26.39999999999999</v>
+        <v>27.63499999999999</v>
       </c>
       <c r="F62">
-        <v>74.09999999999999</v>
+        <v>75.33499999999999</v>
       </c>
       <c r="G62">
         <v>5.34</v>
@@ -6371,28 +6371,28 @@
         <v>11.95</v>
       </c>
       <c r="M62">
-        <v>5.61678</v>
+        <v>5.710393</v>
       </c>
       <c r="N62">
-        <v>6.333219999999999</v>
+        <v>6.239606999999999</v>
       </c>
       <c r="O62">
-        <v>0.6333219999999999</v>
+        <v>0.6239607</v>
       </c>
       <c r="P62">
-        <v>5.699897999999999</v>
+        <v>5.6156463</v>
       </c>
       <c r="Q62">
-        <v>9.449897999999999</v>
+        <v>9.3656463</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1637948895510578</v>
+        <v>0.1666916544336534</v>
       </c>
       <c r="T62">
-        <v>1.825343414483147</v>
+        <v>1.870155445935271</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.127553509306043</v>
+        <v>2.092675582923977</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1066239452291248</v>
+        <v>0.1067979346378265</v>
       </c>
       <c r="C63">
-        <v>42.76700969499288</v>
+        <v>41.33947514613908</v>
       </c>
       <c r="D63">
-        <v>112.7620096949929</v>
+        <v>112.5694751461391</v>
       </c>
       <c r="E63">
-        <v>27.63499999999999</v>
+        <v>28.86999999999999</v>
       </c>
       <c r="F63">
-        <v>75.33499999999999</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="G63">
         <v>5.34</v>
@@ -6453,28 +6453,28 @@
         <v>11.95</v>
       </c>
       <c r="M63">
-        <v>5.710393</v>
+        <v>5.804006</v>
       </c>
       <c r="N63">
-        <v>6.239606999999999</v>
+        <v>6.145993999999999</v>
       </c>
       <c r="O63">
-        <v>0.6239607</v>
+        <v>0.6145993999999999</v>
       </c>
       <c r="P63">
-        <v>5.6156463</v>
+        <v>5.531394599999999</v>
       </c>
       <c r="Q63">
-        <v>9.3656463</v>
+        <v>9.281394599999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1666916544336534</v>
+        <v>0.1697408806258592</v>
       </c>
       <c r="T63">
-        <v>1.870155445935271</v>
+        <v>1.917326005358558</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.092675582923977</v>
+        <v>2.058922750941332</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1067979346378265</v>
+        <v>0.1069719240465282</v>
       </c>
       <c r="C64">
-        <v>41.33947514613908</v>
+        <v>39.91259695959013</v>
       </c>
       <c r="D64">
-        <v>112.5694751461391</v>
+        <v>112.3775969595901</v>
       </c>
       <c r="E64">
-        <v>28.86999999999999</v>
+        <v>30.105</v>
       </c>
       <c r="F64">
-        <v>76.56999999999999</v>
+        <v>77.80500000000001</v>
       </c>
       <c r="G64">
         <v>5.34</v>
@@ -6535,28 +6535,28 @@
         <v>11.95</v>
       </c>
       <c r="M64">
-        <v>5.804006</v>
+        <v>5.897619000000001</v>
       </c>
       <c r="N64">
-        <v>6.145993999999999</v>
+        <v>6.052380999999999</v>
       </c>
       <c r="O64">
-        <v>0.6145993999999999</v>
+        <v>0.6052380999999999</v>
       </c>
       <c r="P64">
-        <v>5.531394599999999</v>
+        <v>5.447142899999998</v>
       </c>
       <c r="Q64">
-        <v>9.281394599999999</v>
+        <v>9.197142899999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1697408806258592</v>
+        <v>0.1729549298554815</v>
       </c>
       <c r="T64">
-        <v>1.917326005358558</v>
+        <v>1.967046324750672</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.058922750941332</v>
+        <v>2.026241437434327</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1069719240465282</v>
+        <v>0.1153251134552299</v>
       </c>
       <c r="C65">
-        <v>39.91259695959013</v>
+        <v>30.17691941004416</v>
       </c>
       <c r="D65">
-        <v>112.3775969595901</v>
+        <v>103.8769194100442</v>
       </c>
       <c r="E65">
-        <v>30.105</v>
+        <v>31.34</v>
       </c>
       <c r="F65">
-        <v>77.80500000000001</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="G65">
         <v>5.34</v>
@@ -6617,45 +6617,45 @@
         <v>11.95</v>
       </c>
       <c r="M65">
-        <v>5.897619000000001</v>
+        <v>7.1136</v>
       </c>
       <c r="N65">
-        <v>6.052380999999999</v>
+        <v>4.836399999999999</v>
       </c>
       <c r="O65">
-        <v>0.6052380999999999</v>
+        <v>0.48364</v>
       </c>
       <c r="P65">
-        <v>5.447142899999998</v>
+        <v>4.352759999999999</v>
       </c>
       <c r="Q65">
-        <v>9.197142899999999</v>
+        <v>8.10276</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1729549298554815</v>
+        <v>0.1763475373756385</v>
       </c>
       <c r="T65">
-        <v>1.967046324750672</v>
+        <v>2.019528884109014</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.1</v>
       </c>
       <c r="W65">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.026241437434327</v>
+        <v>1.679880791722897</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1153251134552299</v>
+        <v>0.1156269028639315</v>
       </c>
       <c r="C66">
-        <v>30.17691941004416</v>
+        <v>28.65880677037713</v>
       </c>
       <c r="D66">
-        <v>103.8769194100442</v>
+        <v>103.5938067703771</v>
       </c>
       <c r="E66">
-        <v>31.34</v>
+        <v>32.575</v>
       </c>
       <c r="F66">
-        <v>79.04000000000001</v>
+        <v>80.27500000000001</v>
       </c>
       <c r="G66">
         <v>5.34</v>
@@ -6699,28 +6699,28 @@
         <v>11.95</v>
       </c>
       <c r="M66">
-        <v>7.1136</v>
+        <v>7.22475</v>
       </c>
       <c r="N66">
-        <v>4.836399999999999</v>
+        <v>4.725249999999999</v>
       </c>
       <c r="O66">
-        <v>0.48364</v>
+        <v>0.4725249999999999</v>
       </c>
       <c r="P66">
-        <v>4.352759999999999</v>
+        <v>4.252724999999999</v>
       </c>
       <c r="Q66">
-        <v>8.10276</v>
+        <v>8.002724999999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1763475373756385</v>
+        <v>0.1799340081826615</v>
       </c>
       <c r="T66">
-        <v>2.019528884109014</v>
+        <v>2.075010446859262</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.679880791722897</v>
+        <v>1.654036471850237</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1156269028639315</v>
+        <v>0.1159286922726332</v>
       </c>
       <c r="C67">
-        <v>28.65880677037713</v>
+        <v>27.14223316185594</v>
       </c>
       <c r="D67">
-        <v>103.5938067703771</v>
+        <v>103.3122331618559</v>
       </c>
       <c r="E67">
-        <v>32.575</v>
+        <v>33.81</v>
       </c>
       <c r="F67">
-        <v>80.27500000000001</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="G67">
         <v>5.34</v>
@@ -6781,28 +6781,28 @@
         <v>11.95</v>
       </c>
       <c r="M67">
-        <v>7.22475</v>
+        <v>7.335900000000001</v>
       </c>
       <c r="N67">
-        <v>4.725249999999999</v>
+        <v>4.614099999999999</v>
       </c>
       <c r="O67">
-        <v>0.4725249999999999</v>
+        <v>0.4614099999999999</v>
       </c>
       <c r="P67">
-        <v>4.252724999999999</v>
+        <v>4.152689999999999</v>
       </c>
       <c r="Q67">
-        <v>8.002724999999998</v>
+        <v>7.902689999999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1799340081826615</v>
+        <v>0.1837314478606859</v>
       </c>
       <c r="T67">
-        <v>2.075010446859262</v>
+        <v>2.133755630947759</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.654036471850237</v>
+        <v>1.628975313185839</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1159286922726332</v>
+        <v>0.1162304816813349</v>
       </c>
       <c r="C68">
-        <v>27.14223316185594</v>
+        <v>25.627186068987</v>
       </c>
       <c r="D68">
-        <v>103.3122331618559</v>
+        <v>103.032186068987</v>
       </c>
       <c r="E68">
-        <v>33.81</v>
+        <v>35.045</v>
       </c>
       <c r="F68">
-        <v>81.51000000000001</v>
+        <v>82.745</v>
       </c>
       <c r="G68">
         <v>5.34</v>
@@ -6863,28 +6863,28 @@
         <v>11.95</v>
       </c>
       <c r="M68">
-        <v>7.335900000000001</v>
+        <v>7.44705</v>
       </c>
       <c r="N68">
-        <v>4.614099999999999</v>
+        <v>4.502949999999999</v>
       </c>
       <c r="O68">
-        <v>0.4614099999999999</v>
+        <v>0.4502949999999999</v>
       </c>
       <c r="P68">
-        <v>4.152689999999999</v>
+        <v>4.052655</v>
       </c>
       <c r="Q68">
-        <v>7.902689999999999</v>
+        <v>7.802655</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1837314478606859</v>
+        <v>0.1877590353979845</v>
       </c>
       <c r="T68">
-        <v>2.133755630947759</v>
+        <v>2.196061129223439</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.628975313185839</v>
+        <v>1.604662248809931</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1162304816813349</v>
+        <v>0.1165322710900366</v>
       </c>
       <c r="C69">
-        <v>25.627186068987</v>
+        <v>24.11365311161218</v>
       </c>
       <c r="D69">
-        <v>103.032186068987</v>
+        <v>102.7536531116122</v>
       </c>
       <c r="E69">
-        <v>35.045</v>
+        <v>36.28</v>
       </c>
       <c r="F69">
-        <v>82.745</v>
+        <v>83.98</v>
       </c>
       <c r="G69">
         <v>5.34</v>
@@ -6945,28 +6945,28 @@
         <v>11.95</v>
       </c>
       <c r="M69">
-        <v>7.44705</v>
+        <v>7.5582</v>
       </c>
       <c r="N69">
-        <v>4.502949999999999</v>
+        <v>4.391799999999999</v>
       </c>
       <c r="O69">
-        <v>0.4502949999999999</v>
+        <v>0.4391799999999999</v>
       </c>
       <c r="P69">
-        <v>4.052655</v>
+        <v>3.952619999999999</v>
       </c>
       <c r="Q69">
-        <v>7.802655</v>
+        <v>7.70262</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1877590353979845</v>
+        <v>0.1920383471563643</v>
       </c>
       <c r="T69">
-        <v>2.196061129223439</v>
+        <v>2.262260721141348</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.604662248809931</v>
+        <v>1.581064274562726</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1165322710900366</v>
+        <v>0.1168340604987382</v>
       </c>
       <c r="C70">
-        <v>24.11365311161218</v>
+        <v>22.60162204308442</v>
       </c>
       <c r="D70">
-        <v>102.7536531116122</v>
+        <v>102.4766220430844</v>
       </c>
       <c r="E70">
-        <v>36.28</v>
+        <v>37.515</v>
       </c>
       <c r="F70">
-        <v>83.98</v>
+        <v>85.215</v>
       </c>
       <c r="G70">
         <v>5.34</v>
@@ -7027,28 +7027,28 @@
         <v>11.95</v>
       </c>
       <c r="M70">
-        <v>7.5582</v>
+        <v>7.66935</v>
       </c>
       <c r="N70">
-        <v>4.391799999999999</v>
+        <v>4.28065</v>
       </c>
       <c r="O70">
-        <v>0.4391799999999999</v>
+        <v>0.428065</v>
       </c>
       <c r="P70">
-        <v>3.952619999999999</v>
+        <v>3.852584999999999</v>
       </c>
       <c r="Q70">
-        <v>7.70262</v>
+        <v>7.602584999999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1920383471563643</v>
+        <v>0.1965937435443169</v>
       </c>
       <c r="T70">
-        <v>2.262260721141348</v>
+        <v>2.332731254473316</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.581064274562726</v>
+        <v>1.558150299569064</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1168340604987382</v>
+        <v>0.1171358499074399</v>
       </c>
       <c r="C71">
-        <v>22.60162204308442</v>
+        <v>21.09108074847285</v>
       </c>
       <c r="D71">
-        <v>102.4766220430844</v>
+        <v>102.2010807484728</v>
       </c>
       <c r="E71">
-        <v>37.515</v>
+        <v>38.75</v>
       </c>
       <c r="F71">
-        <v>85.215</v>
+        <v>86.45</v>
       </c>
       <c r="G71">
         <v>5.34</v>
@@ -7109,28 +7109,28 @@
         <v>11.95</v>
       </c>
       <c r="M71">
-        <v>7.66935</v>
+        <v>7.7805</v>
       </c>
       <c r="N71">
-        <v>4.28065</v>
+        <v>4.169499999999999</v>
       </c>
       <c r="O71">
-        <v>0.428065</v>
+        <v>0.4169499999999999</v>
       </c>
       <c r="P71">
-        <v>3.852584999999999</v>
+        <v>3.752549999999999</v>
       </c>
       <c r="Q71">
-        <v>7.602584999999999</v>
+        <v>7.502549999999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1965937435443169</v>
+        <v>0.2014528330247997</v>
       </c>
       <c r="T71">
-        <v>2.332731254473316</v>
+        <v>2.407899823360748</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.558150299569064</v>
+        <v>1.53589100957522</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1171358499074399</v>
+        <v>0.1174376393161416</v>
       </c>
       <c r="C72">
-        <v>21.09108074847285</v>
+        <v>19.58201724279671</v>
       </c>
       <c r="D72">
-        <v>102.2010807484728</v>
+        <v>101.9270172427967</v>
       </c>
       <c r="E72">
-        <v>38.75</v>
+        <v>39.985</v>
       </c>
       <c r="F72">
-        <v>86.45</v>
+        <v>87.685</v>
       </c>
       <c r="G72">
         <v>5.34</v>
@@ -7191,28 +7191,28 @@
         <v>11.95</v>
       </c>
       <c r="M72">
-        <v>7.7805</v>
+        <v>7.89165</v>
       </c>
       <c r="N72">
-        <v>4.169499999999999</v>
+        <v>4.058349999999999</v>
       </c>
       <c r="O72">
-        <v>0.4169499999999999</v>
+        <v>0.4058349999999999</v>
       </c>
       <c r="P72">
-        <v>3.752549999999999</v>
+        <v>3.652514999999999</v>
       </c>
       <c r="Q72">
-        <v>7.502549999999999</v>
+        <v>7.402514999999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2014528330247997</v>
+        <v>0.2066470321246262</v>
       </c>
       <c r="T72">
-        <v>2.407899823360748</v>
+        <v>2.488252431481797</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.53589100957522</v>
+        <v>1.514258741834724</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1174376393161416</v>
+        <v>0.1557449181744328</v>
       </c>
       <c r="C73">
-        <v>19.58201724279671</v>
+        <v>-7.537026274904818</v>
       </c>
       <c r="D73">
-        <v>101.9270172427967</v>
+        <v>76.04297372509518</v>
       </c>
       <c r="E73">
-        <v>39.985</v>
+        <v>41.22</v>
       </c>
       <c r="F73">
-        <v>87.685</v>
+        <v>88.92</v>
       </c>
       <c r="G73">
         <v>5.34</v>
@@ -7273,45 +7273,45 @@
         <v>11.95</v>
       </c>
       <c r="M73">
-        <v>7.89165</v>
+        <v>13.053456</v>
       </c>
       <c r="N73">
-        <v>4.058349999999999</v>
+        <v>-1.103456000000001</v>
       </c>
       <c r="O73">
-        <v>0.4058349999999999</v>
+        <v>-0.1103456000000001</v>
       </c>
       <c r="P73">
-        <v>3.652514999999999</v>
+        <v>-0.9931104000000012</v>
       </c>
       <c r="Q73">
-        <v>7.402514999999999</v>
+        <v>2.756889599999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2066470321246262</v>
+        <v>0.2133036840527024</v>
       </c>
       <c r="T73">
-        <v>2.488252431481796</v>
+        <v>2.591228719740134</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1</v>
+        <v>0.09154663715111155</v>
       </c>
       <c r="W73">
-        <v>0.081</v>
+        <v>0.1333609536662168</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.514258741834724</v>
+        <v>0.9154663715111154</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1557449181744328</v>
+        <v>0.1567549181744328</v>
       </c>
       <c r="C74">
-        <v>-7.537026274904818</v>
+        <v>-9.27778553390182</v>
       </c>
       <c r="D74">
-        <v>76.04297372509518</v>
+        <v>75.53721446609818</v>
       </c>
       <c r="E74">
-        <v>41.22</v>
+        <v>42.455</v>
       </c>
       <c r="F74">
-        <v>88.92</v>
+        <v>90.155</v>
       </c>
       <c r="G74">
         <v>5.34</v>
@@ -7355,37 +7355,37 @@
         <v>11.95</v>
       </c>
       <c r="M74">
-        <v>13.053456</v>
+        <v>13.234754</v>
       </c>
       <c r="N74">
-        <v>-1.103456000000001</v>
+        <v>-1.284754000000001</v>
       </c>
       <c r="O74">
-        <v>-0.1103456000000001</v>
+        <v>-0.1284754000000001</v>
       </c>
       <c r="P74">
-        <v>-0.9931104000000012</v>
+        <v>-1.156278600000001</v>
       </c>
       <c r="Q74">
-        <v>2.756889599999999</v>
+        <v>2.593721399999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2133036840527024</v>
+        <v>0.2195075242028025</v>
       </c>
       <c r="T74">
-        <v>2.591228719740134</v>
+        <v>2.687200153804584</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.09154663715111155</v>
+        <v>0.09029257362849358</v>
       </c>
       <c r="W74">
-        <v>0.1333609536662168</v>
+        <v>0.1335450501913371</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9154663715111154</v>
+        <v>0.9029257362849358</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1567549181744328</v>
+        <v>0.1577649181744328</v>
       </c>
       <c r="C75">
-        <v>-9.27778553390182</v>
+        <v>-11.01186166652718</v>
       </c>
       <c r="D75">
-        <v>75.53721446609818</v>
+        <v>75.03813833347282</v>
       </c>
       <c r="E75">
-        <v>42.455</v>
+        <v>43.69</v>
       </c>
       <c r="F75">
-        <v>90.155</v>
+        <v>91.39</v>
       </c>
       <c r="G75">
         <v>5.34</v>
@@ -7437,37 +7437,37 @@
         <v>11.95</v>
       </c>
       <c r="M75">
-        <v>13.234754</v>
+        <v>13.416052</v>
       </c>
       <c r="N75">
-        <v>-1.284754000000001</v>
+        <v>-1.466052000000001</v>
       </c>
       <c r="O75">
-        <v>-0.1284754000000001</v>
+        <v>-0.1466052000000001</v>
       </c>
       <c r="P75">
-        <v>-1.156278600000001</v>
+        <v>-1.319446800000001</v>
       </c>
       <c r="Q75">
-        <v>2.593721399999999</v>
+        <v>2.430553199999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2195075242028025</v>
+        <v>0.2261885828259872</v>
       </c>
       <c r="T75">
-        <v>2.687200153804584</v>
+        <v>2.790554005873991</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.09029257362849358</v>
+        <v>0.08907240371459502</v>
       </c>
       <c r="W75">
-        <v>0.1335450501913371</v>
+        <v>0.1337241711346975</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9029257362849358</v>
+        <v>0.8907240371459502</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1577649181744328</v>
+        <v>0.1587749181744328</v>
       </c>
       <c r="C76">
-        <v>-11.01186166652718</v>
+        <v>-12.73938627002886</v>
       </c>
       <c r="D76">
-        <v>75.03813833347282</v>
+        <v>74.54561372997114</v>
       </c>
       <c r="E76">
-        <v>43.69</v>
+        <v>44.925</v>
       </c>
       <c r="F76">
-        <v>91.39</v>
+        <v>92.625</v>
       </c>
       <c r="G76">
         <v>5.34</v>
@@ -7519,37 +7519,37 @@
         <v>11.95</v>
       </c>
       <c r="M76">
-        <v>13.416052</v>
+        <v>13.59735</v>
       </c>
       <c r="N76">
-        <v>-1.466052000000001</v>
+        <v>-1.647350000000001</v>
       </c>
       <c r="O76">
-        <v>-0.1466052000000001</v>
+        <v>-0.1647350000000001</v>
       </c>
       <c r="P76">
-        <v>-1.319446800000001</v>
+        <v>-1.482615000000001</v>
       </c>
       <c r="Q76">
-        <v>2.430553199999999</v>
+        <v>2.267384999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2261885828259872</v>
+        <v>0.2334041261390267</v>
       </c>
       <c r="T76">
-        <v>2.790554005873991</v>
+        <v>2.90217616610895</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.08907240371459502</v>
+        <v>0.08788477166506709</v>
       </c>
       <c r="W76">
-        <v>0.1337241711346975</v>
+        <v>0.1338985155195682</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8907240371459502</v>
+        <v>0.8788477166506709</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1587749181744328</v>
+        <v>0.1597849181744328</v>
       </c>
       <c r="C77">
-        <v>-12.73938627002886</v>
+        <v>-14.46048750914791</v>
       </c>
       <c r="D77">
-        <v>74.54561372997114</v>
+        <v>74.05951249085209</v>
       </c>
       <c r="E77">
-        <v>44.925</v>
+        <v>46.16</v>
       </c>
       <c r="F77">
-        <v>92.625</v>
+        <v>93.86</v>
       </c>
       <c r="G77">
         <v>5.34</v>
@@ -7601,37 +7601,37 @@
         <v>11.95</v>
       </c>
       <c r="M77">
-        <v>13.59735</v>
+        <v>13.778648</v>
       </c>
       <c r="N77">
-        <v>-1.647350000000001</v>
+        <v>-1.828648000000001</v>
       </c>
       <c r="O77">
-        <v>-0.1647350000000001</v>
+        <v>-0.1828648000000001</v>
       </c>
       <c r="P77">
-        <v>-1.482615000000001</v>
+        <v>-1.645783200000001</v>
       </c>
       <c r="Q77">
-        <v>2.267384999999999</v>
+        <v>2.104216799999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2334041261390267</v>
+        <v>0.2412209647281529</v>
       </c>
       <c r="T77">
-        <v>2.90217616610895</v>
+        <v>3.023100173030157</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.08788477166506709</v>
+        <v>0.08672839309052673</v>
       </c>
       <c r="W77">
-        <v>0.1338985155195682</v>
+        <v>0.1340682718943107</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8788477166506709</v>
+        <v>0.8672839309052672</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1597849181744328</v>
+        <v>0.1607949181744328</v>
       </c>
       <c r="C78">
-        <v>-14.46048750914791</v>
+        <v>-16.17529022730761</v>
       </c>
       <c r="D78">
-        <v>74.05951249085209</v>
+        <v>73.57970977269238</v>
       </c>
       <c r="E78">
-        <v>46.16</v>
+        <v>47.395</v>
       </c>
       <c r="F78">
-        <v>93.86</v>
+        <v>95.095</v>
       </c>
       <c r="G78">
         <v>5.34</v>
@@ -7683,37 +7683,37 @@
         <v>11.95</v>
       </c>
       <c r="M78">
-        <v>13.778648</v>
+        <v>13.959946</v>
       </c>
       <c r="N78">
-        <v>-1.828648000000001</v>
+        <v>-2.009946000000001</v>
       </c>
       <c r="O78">
-        <v>-0.1828648000000001</v>
+        <v>-0.2009946000000001</v>
       </c>
       <c r="P78">
-        <v>-1.645783200000001</v>
+        <v>-1.808951400000001</v>
       </c>
       <c r="Q78">
-        <v>2.104216799999999</v>
+        <v>1.941048599999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2412209647281529</v>
+        <v>0.2497175284119856</v>
       </c>
       <c r="T78">
-        <v>3.023100173030157</v>
+        <v>3.15453931098799</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.08672839309052673</v>
+        <v>0.0856020503231173</v>
       </c>
       <c r="W78">
-        <v>0.1340682718943107</v>
+        <v>0.1342336190125664</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8672839309052672</v>
+        <v>0.8560205032311728</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1607949181744328</v>
+        <v>0.1618049181744328</v>
       </c>
       <c r="C79">
-        <v>-16.17529022730761</v>
+        <v>-17.88391605350881</v>
       </c>
       <c r="D79">
-        <v>73.57970977269238</v>
+        <v>73.10608394649118</v>
       </c>
       <c r="E79">
-        <v>47.395</v>
+        <v>48.63</v>
       </c>
       <c r="F79">
-        <v>95.095</v>
+        <v>96.33</v>
       </c>
       <c r="G79">
         <v>5.34</v>
@@ -7765,37 +7765,37 @@
         <v>11.95</v>
       </c>
       <c r="M79">
-        <v>13.959946</v>
+        <v>14.141244</v>
       </c>
       <c r="N79">
-        <v>-2.009946000000001</v>
+        <v>-2.191244000000001</v>
       </c>
       <c r="O79">
-        <v>-0.2009946000000001</v>
+        <v>-0.2191244000000001</v>
       </c>
       <c r="P79">
-        <v>-1.808951400000001</v>
+        <v>-1.972119600000001</v>
       </c>
       <c r="Q79">
-        <v>1.941048599999999</v>
+        <v>1.777880399999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2497175284119856</v>
+        <v>0.2589865069761667</v>
       </c>
       <c r="T79">
-        <v>3.15453931098799</v>
+        <v>3.297927461487444</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.0856020503231173</v>
+        <v>0.08450458813948758</v>
       </c>
       <c r="W79">
-        <v>0.1342336190125664</v>
+        <v>0.1343947264611232</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8560205032311728</v>
+        <v>0.8450458813948758</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1618049181744328</v>
+        <v>0.1628149181744328</v>
       </c>
       <c r="C80">
-        <v>-17.88391605350881</v>
+        <v>-19.58648350512283</v>
       </c>
       <c r="D80">
-        <v>73.10608394649118</v>
+        <v>72.63851649487717</v>
       </c>
       <c r="E80">
-        <v>48.63</v>
+        <v>49.86499999999999</v>
       </c>
       <c r="F80">
-        <v>96.33</v>
+        <v>97.565</v>
       </c>
       <c r="G80">
         <v>5.34</v>
@@ -7847,37 +7847,37 @@
         <v>11.95</v>
       </c>
       <c r="M80">
-        <v>14.141244</v>
+        <v>14.322542</v>
       </c>
       <c r="N80">
-        <v>-2.191244000000001</v>
+        <v>-2.372542000000001</v>
       </c>
       <c r="O80">
-        <v>-0.2191244000000001</v>
+        <v>-0.2372542000000001</v>
       </c>
       <c r="P80">
-        <v>-1.972119600000001</v>
+        <v>-2.135287800000001</v>
       </c>
       <c r="Q80">
-        <v>1.777880399999999</v>
+        <v>1.614712199999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2589865069761667</v>
+        <v>0.2691382454036033</v>
       </c>
       <c r="T80">
-        <v>3.297927461487444</v>
+        <v>3.45497162632018</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.08450458813948758</v>
+        <v>0.083434909808608</v>
       </c>
       <c r="W80">
-        <v>0.1343947264611232</v>
+        <v>0.1345517552400964</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8450458813948758</v>
+        <v>0.8343490980860799</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1628149181744328</v>
+        <v>0.1638249181744328</v>
       </c>
       <c r="C81">
-        <v>-19.58648350512283</v>
+        <v>-21.28310808676495</v>
       </c>
       <c r="D81">
-        <v>72.63851649487717</v>
+        <v>72.17689191323505</v>
       </c>
       <c r="E81">
-        <v>49.86499999999999</v>
+        <v>51.10000000000001</v>
       </c>
       <c r="F81">
-        <v>97.565</v>
+        <v>98.80000000000001</v>
       </c>
       <c r="G81">
         <v>5.34</v>
@@ -7929,37 +7929,37 @@
         <v>11.95</v>
       </c>
       <c r="M81">
-        <v>14.322542</v>
+        <v>14.50384</v>
       </c>
       <c r="N81">
-        <v>-2.372542000000001</v>
+        <v>-2.553840000000005</v>
       </c>
       <c r="O81">
-        <v>-0.2372542000000001</v>
+        <v>-0.2553840000000004</v>
       </c>
       <c r="P81">
-        <v>-2.135287800000001</v>
+        <v>-2.298456000000004</v>
       </c>
       <c r="Q81">
-        <v>1.614712199999999</v>
+        <v>1.451543999999996</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2691382454036033</v>
+        <v>0.2803051576737834</v>
       </c>
       <c r="T81">
-        <v>3.45497162632018</v>
+        <v>3.627720207636189</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.083434909808608</v>
+        <v>0.08239197343600037</v>
       </c>
       <c r="W81">
-        <v>0.1345517552400964</v>
+        <v>0.1347048582995952</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8343490980860799</v>
+        <v>0.8239197343600038</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1638249181744328</v>
+        <v>0.1648349181744328</v>
       </c>
       <c r="C82">
-        <v>-21.28310808676495</v>
+        <v>-22.97390238542158</v>
       </c>
       <c r="D82">
-        <v>72.17689191323505</v>
+        <v>71.72109761457843</v>
       </c>
       <c r="E82">
-        <v>51.10000000000001</v>
+        <v>52.33500000000001</v>
       </c>
       <c r="F82">
-        <v>98.80000000000001</v>
+        <v>100.035</v>
       </c>
       <c r="G82">
         <v>5.34</v>
@@ -8011,37 +8011,37 @@
         <v>11.95</v>
       </c>
       <c r="M82">
-        <v>14.50384</v>
+        <v>14.685138</v>
       </c>
       <c r="N82">
-        <v>-2.553840000000005</v>
+        <v>-2.735138000000005</v>
       </c>
       <c r="O82">
-        <v>-0.2553840000000004</v>
+        <v>-0.2735138000000005</v>
       </c>
       <c r="P82">
-        <v>-2.298456000000004</v>
+        <v>-2.461624200000004</v>
       </c>
       <c r="Q82">
-        <v>1.451543999999996</v>
+        <v>1.288375799999996</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2803051576737834</v>
+        <v>0.2926475343934563</v>
       </c>
       <c r="T82">
-        <v>3.627720207636189</v>
+        <v>3.818652850143357</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.08239197343600037</v>
+        <v>0.0813747885787658</v>
       </c>
       <c r="W82">
-        <v>0.1347048582995952</v>
+        <v>0.1348541810366372</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8239197343600038</v>
+        <v>0.813747885787658</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1648349181744328</v>
+        <v>0.1658449181744328</v>
       </c>
       <c r="C83">
-        <v>-22.97390238542158</v>
+        <v>-24.65897616199589</v>
       </c>
       <c r="D83">
-        <v>71.72109761457843</v>
+        <v>71.27102383800411</v>
       </c>
       <c r="E83">
-        <v>52.33500000000001</v>
+        <v>53.57000000000001</v>
       </c>
       <c r="F83">
-        <v>100.035</v>
+        <v>101.27</v>
       </c>
       <c r="G83">
         <v>5.34</v>
@@ -8093,37 +8093,37 @@
         <v>11.95</v>
       </c>
       <c r="M83">
-        <v>14.685138</v>
+        <v>14.866436</v>
       </c>
       <c r="N83">
-        <v>-2.735138000000005</v>
+        <v>-2.916436000000004</v>
       </c>
       <c r="O83">
-        <v>-0.2735138000000005</v>
+        <v>-0.2916436000000004</v>
       </c>
       <c r="P83">
-        <v>-2.461624200000004</v>
+        <v>-2.624792400000004</v>
       </c>
       <c r="Q83">
-        <v>1.288375799999996</v>
+        <v>1.125207599999996</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2926475343934563</v>
+        <v>0.3063612863042039</v>
       </c>
       <c r="T83">
-        <v>3.818652850143357</v>
+        <v>4.030800230706877</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.0813747885787658</v>
+        <v>0.08038241310829305</v>
       </c>
       <c r="W83">
-        <v>0.1348541810366372</v>
+        <v>0.1349998617557026</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.813747885787658</v>
+        <v>0.8038241310829305</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1658449181744328</v>
+        <v>0.2125649392263878</v>
       </c>
       <c r="C84">
-        <v>-24.65897616199589</v>
+        <v>-41.92817159037077</v>
       </c>
       <c r="D84">
-        <v>71.27102383800411</v>
+        <v>55.23682840962925</v>
       </c>
       <c r="E84">
-        <v>53.57000000000001</v>
+        <v>54.80500000000001</v>
       </c>
       <c r="F84">
-        <v>101.27</v>
+        <v>102.505</v>
       </c>
       <c r="G84">
         <v>5.34</v>
@@ -8175,45 +8175,45 @@
         <v>11.95</v>
       </c>
       <c r="M84">
-        <v>14.866436</v>
+        <v>20.583004</v>
       </c>
       <c r="N84">
-        <v>-2.916436000000004</v>
+        <v>-8.633004000000003</v>
       </c>
       <c r="O84">
-        <v>-0.2916436000000004</v>
+        <v>-0.8633004000000004</v>
       </c>
       <c r="P84">
-        <v>-2.624792400000004</v>
+        <v>-7.769703600000003</v>
       </c>
       <c r="Q84">
-        <v>1.125207599999996</v>
+        <v>-4.019703600000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3063612863042039</v>
+        <v>0.3269238387453626</v>
       </c>
       <c r="T84">
-        <v>4.030800230706877</v>
+        <v>4.348896377296279</v>
       </c>
       <c r="U84">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.08038241310829305</v>
+        <v>0.05805760908368865</v>
       </c>
       <c r="W84">
-        <v>0.1349998617557026</v>
+        <v>0.1891420320959953</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8038241310829305</v>
+        <v>0.5805760908368864</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2125649392263878</v>
+        <v>0.2141149392263877</v>
       </c>
       <c r="C85">
-        <v>-41.92817159037077</v>
+        <v>-43.57239654229301</v>
       </c>
       <c r="D85">
-        <v>55.23682840962925</v>
+        <v>54.827603457707</v>
       </c>
       <c r="E85">
-        <v>54.80500000000001</v>
+        <v>56.04000000000001</v>
       </c>
       <c r="F85">
-        <v>102.505</v>
+        <v>103.74</v>
       </c>
       <c r="G85">
         <v>5.34</v>
@@ -8257,37 +8257,37 @@
         <v>11.95</v>
       </c>
       <c r="M85">
-        <v>20.583004</v>
+        <v>20.830992</v>
       </c>
       <c r="N85">
-        <v>-8.633004000000003</v>
+        <v>-8.880992000000003</v>
       </c>
       <c r="O85">
-        <v>-0.8633004000000004</v>
+        <v>-0.8880992000000003</v>
       </c>
       <c r="P85">
-        <v>-7.769703600000003</v>
+        <v>-7.992892800000003</v>
       </c>
       <c r="Q85">
-        <v>-4.019703600000003</v>
+        <v>-4.242892800000003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3269238387453626</v>
+        <v>0.3444940786669479</v>
       </c>
       <c r="T85">
-        <v>4.348896377296279</v>
+        <v>4.620702400877296</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.05805760908368865</v>
+        <v>0.0573664470707876</v>
       </c>
       <c r="W85">
-        <v>0.1891420320959953</v>
+        <v>0.1892808174281858</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5805760908368864</v>
+        <v>0.573664470707876</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2141149392263877</v>
+        <v>0.2156649392263878</v>
       </c>
       <c r="C86">
-        <v>-43.57239654229299</v>
+        <v>-45.21060255662098</v>
       </c>
       <c r="D86">
-        <v>54.827603457707</v>
+        <v>54.42439744337901</v>
       </c>
       <c r="E86">
-        <v>56.03999999999999</v>
+        <v>57.27499999999999</v>
       </c>
       <c r="F86">
-        <v>103.74</v>
+        <v>104.975</v>
       </c>
       <c r="G86">
         <v>5.34</v>
@@ -8339,37 +8339,37 @@
         <v>11.95</v>
       </c>
       <c r="M86">
-        <v>20.830992</v>
+        <v>21.07898</v>
       </c>
       <c r="N86">
-        <v>-8.880991999999999</v>
+        <v>-9.128979999999999</v>
       </c>
       <c r="O86">
-        <v>-0.8880992</v>
+        <v>-0.9128979999999999</v>
       </c>
       <c r="P86">
-        <v>-7.992892799999999</v>
+        <v>-8.216081999999998</v>
       </c>
       <c r="Q86">
-        <v>-4.242892799999999</v>
+        <v>-4.466081999999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3444940786669476</v>
+        <v>0.3644070172447442</v>
       </c>
       <c r="T86">
-        <v>4.620702400877293</v>
+        <v>4.928749227602447</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.05736644707078761</v>
+        <v>0.05669154769348422</v>
       </c>
       <c r="W86">
-        <v>0.1892808174281858</v>
+        <v>0.1894163372231484</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.573664470707876</v>
+        <v>0.5669154769348422</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2156649392263878</v>
+        <v>0.2172149392263877</v>
       </c>
       <c r="C87">
-        <v>-45.21060255662098</v>
+        <v>-46.84292145498794</v>
       </c>
       <c r="D87">
-        <v>54.42439744337901</v>
+        <v>54.02707854501205</v>
       </c>
       <c r="E87">
-        <v>57.27499999999999</v>
+        <v>58.50999999999999</v>
       </c>
       <c r="F87">
-        <v>104.975</v>
+        <v>106.21</v>
       </c>
       <c r="G87">
         <v>5.34</v>
@@ -8421,37 +8421,37 @@
         <v>11.95</v>
       </c>
       <c r="M87">
-        <v>21.07898</v>
+        <v>21.326968</v>
       </c>
       <c r="N87">
-        <v>-9.128979999999999</v>
+        <v>-9.376968000000002</v>
       </c>
       <c r="O87">
-        <v>-0.9128979999999999</v>
+        <v>-0.9376968000000002</v>
       </c>
       <c r="P87">
-        <v>-8.216081999999998</v>
+        <v>-8.439271200000002</v>
       </c>
       <c r="Q87">
-        <v>-4.466081999999998</v>
+        <v>-4.689271200000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3644070172447442</v>
+        <v>0.3871646613336545</v>
       </c>
       <c r="T87">
-        <v>4.928749227602447</v>
+        <v>5.280802743859764</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.05669154769348422</v>
+        <v>0.05603234365053672</v>
       </c>
       <c r="W87">
-        <v>0.1894163372231484</v>
+        <v>0.1895487053949722</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5669154769348422</v>
+        <v>0.5603234365053673</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2172149392263877</v>
+        <v>0.2187649392263877</v>
       </c>
       <c r="C88">
-        <v>-46.84292145498794</v>
+        <v>-48.46948123753245</v>
       </c>
       <c r="D88">
-        <v>54.02707854501205</v>
+        <v>53.63551876246755</v>
       </c>
       <c r="E88">
-        <v>58.50999999999999</v>
+        <v>59.74499999999999</v>
       </c>
       <c r="F88">
-        <v>106.21</v>
+        <v>107.445</v>
       </c>
       <c r="G88">
         <v>5.34</v>
@@ -8503,37 +8503,37 @@
         <v>11.95</v>
       </c>
       <c r="M88">
-        <v>21.326968</v>
+        <v>21.574956</v>
       </c>
       <c r="N88">
-        <v>-9.376968000000002</v>
+        <v>-9.624956000000001</v>
       </c>
       <c r="O88">
-        <v>-0.9376968000000002</v>
+        <v>-0.9624956000000001</v>
       </c>
       <c r="P88">
-        <v>-8.439271200000002</v>
+        <v>-8.662460400000001</v>
       </c>
       <c r="Q88">
-        <v>-4.689271200000002</v>
+        <v>-4.912460400000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3871646613336545</v>
+        <v>0.4134234814362432</v>
       </c>
       <c r="T88">
-        <v>5.280802743859764</v>
+        <v>5.687018339541284</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.05603234365053672</v>
+        <v>0.05538829372351907</v>
       </c>
       <c r="W88">
-        <v>0.1895487053949722</v>
+        <v>0.1896780306203174</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5603234365053673</v>
+        <v>0.5538829372351906</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2187649392263877</v>
+        <v>0.2203149392263878</v>
       </c>
       <c r="C89">
-        <v>-48.46948123753245</v>
+        <v>-50.09040622038269</v>
       </c>
       <c r="D89">
-        <v>53.63551876246755</v>
+        <v>53.24959377961732</v>
       </c>
       <c r="E89">
-        <v>59.74499999999999</v>
+        <v>60.98</v>
       </c>
       <c r="F89">
-        <v>107.445</v>
+        <v>108.68</v>
       </c>
       <c r="G89">
         <v>5.34</v>
@@ -8585,37 +8585,37 @@
         <v>11.95</v>
       </c>
       <c r="M89">
-        <v>21.574956</v>
+        <v>21.822944</v>
       </c>
       <c r="N89">
-        <v>-9.624956000000001</v>
+        <v>-9.872944000000004</v>
       </c>
       <c r="O89">
-        <v>-0.9624956000000001</v>
+        <v>-0.9872944000000005</v>
       </c>
       <c r="P89">
-        <v>-8.662460400000001</v>
+        <v>-8.885649600000004</v>
       </c>
       <c r="Q89">
-        <v>-4.912460400000001</v>
+        <v>-5.135649600000004</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4134234814362432</v>
+        <v>0.4440587715559303</v>
       </c>
       <c r="T89">
-        <v>5.687018339541284</v>
+        <v>6.160936534503059</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.05538829372351907</v>
+        <v>0.0547588812948427</v>
       </c>
       <c r="W89">
-        <v>0.1896780306203174</v>
+        <v>0.1898044166359956</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5538829372351906</v>
+        <v>0.547588812948427</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2203149392263878</v>
+        <v>0.2218649392263877</v>
       </c>
       <c r="C90">
-        <v>-50.09040622038269</v>
+        <v>-51.70581716724783</v>
       </c>
       <c r="D90">
-        <v>53.24959377961732</v>
+        <v>52.86918283275218</v>
       </c>
       <c r="E90">
-        <v>60.98</v>
+        <v>62.215</v>
       </c>
       <c r="F90">
-        <v>108.68</v>
+        <v>109.915</v>
       </c>
       <c r="G90">
         <v>5.34</v>
@@ -8667,37 +8667,37 @@
         <v>11.95</v>
       </c>
       <c r="M90">
-        <v>21.822944</v>
+        <v>22.070932</v>
       </c>
       <c r="N90">
-        <v>-9.872944000000004</v>
+        <v>-10.120932</v>
       </c>
       <c r="O90">
-        <v>-0.9872944000000005</v>
+        <v>-1.0120932</v>
       </c>
       <c r="P90">
-        <v>-8.885649600000004</v>
+        <v>-9.108838800000003</v>
       </c>
       <c r="Q90">
-        <v>-5.135649600000004</v>
+        <v>-5.358838800000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4440587715559303</v>
+        <v>0.4802641144246512</v>
       </c>
       <c r="T90">
-        <v>6.160936534503059</v>
+        <v>6.721021674003337</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.0547588812948427</v>
+        <v>0.05414361296568718</v>
       </c>
       <c r="W90">
-        <v>0.1898044166359956</v>
+        <v>0.18992796251649</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.547588812948427</v>
+        <v>0.5414361296568717</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2218649392263877</v>
+        <v>0.2234149392263877</v>
       </c>
       <c r="C91">
-        <v>-51.70581716724783</v>
+        <v>-53.31583141540924</v>
       </c>
       <c r="D91">
-        <v>52.86918283275218</v>
+        <v>52.49416858459077</v>
       </c>
       <c r="E91">
-        <v>62.215</v>
+        <v>63.45</v>
       </c>
       <c r="F91">
-        <v>109.915</v>
+        <v>111.15</v>
       </c>
       <c r="G91">
         <v>5.34</v>
@@ -8749,37 +8749,37 @@
         <v>11.95</v>
       </c>
       <c r="M91">
-        <v>22.070932</v>
+        <v>22.31892</v>
       </c>
       <c r="N91">
-        <v>-10.120932</v>
+        <v>-10.36892</v>
       </c>
       <c r="O91">
-        <v>-1.0120932</v>
+        <v>-1.036892</v>
       </c>
       <c r="P91">
-        <v>-9.108838800000003</v>
+        <v>-9.332028000000003</v>
       </c>
       <c r="Q91">
-        <v>-5.358838800000003</v>
+        <v>-5.582028000000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4802641144246512</v>
+        <v>0.5237105258671163</v>
       </c>
       <c r="T91">
-        <v>6.721021674003337</v>
+        <v>7.393123841403671</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.05414361296568718</v>
+        <v>0.05354201726606842</v>
       </c>
       <c r="W91">
-        <v>0.18992796251649</v>
+        <v>0.1900487629329735</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5414361296568717</v>
+        <v>0.5354201726606842</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2234149392263877</v>
+        <v>0.2249649392263877</v>
       </c>
       <c r="C92">
-        <v>-53.31583141540924</v>
+        <v>-54.92056299638681</v>
       </c>
       <c r="D92">
-        <v>52.49416858459077</v>
+        <v>52.1244370036132</v>
       </c>
       <c r="E92">
-        <v>63.45</v>
+        <v>64.685</v>
       </c>
       <c r="F92">
-        <v>111.15</v>
+        <v>112.385</v>
       </c>
       <c r="G92">
         <v>5.34</v>
@@ -8831,37 +8831,37 @@
         <v>11.95</v>
       </c>
       <c r="M92">
-        <v>22.31892</v>
+        <v>22.566908</v>
       </c>
       <c r="N92">
-        <v>-10.36892</v>
+        <v>-10.616908</v>
       </c>
       <c r="O92">
-        <v>-1.036892</v>
+        <v>-1.0616908</v>
       </c>
       <c r="P92">
-        <v>-9.332028000000003</v>
+        <v>-9.555217200000001</v>
       </c>
       <c r="Q92">
-        <v>-5.582028000000003</v>
+        <v>-5.805217200000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5237105258671163</v>
+        <v>0.5768116954079071</v>
       </c>
       <c r="T92">
-        <v>7.393123841403671</v>
+        <v>8.214582046004081</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.05354201726606842</v>
+        <v>0.05295364344995778</v>
       </c>
       <c r="W92">
-        <v>0.1900487629329735</v>
+        <v>0.1901669083952485</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5354201726606842</v>
+        <v>0.5295364344995779</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2249649392263877</v>
+        <v>0.2265149392263878</v>
       </c>
       <c r="C93">
-        <v>-54.92056299638681</v>
+        <v>-56.52012275154209</v>
       </c>
       <c r="D93">
-        <v>52.1244370036132</v>
+        <v>51.75987724845792</v>
       </c>
       <c r="E93">
-        <v>64.685</v>
+        <v>65.92</v>
       </c>
       <c r="F93">
-        <v>112.385</v>
+        <v>113.62</v>
       </c>
       <c r="G93">
         <v>5.34</v>
@@ -8913,37 +8913,37 @@
         <v>11.95</v>
       </c>
       <c r="M93">
-        <v>22.566908</v>
+        <v>22.814896</v>
       </c>
       <c r="N93">
-        <v>-10.616908</v>
+        <v>-10.864896</v>
       </c>
       <c r="O93">
-        <v>-1.0616908</v>
+        <v>-1.0864896</v>
       </c>
       <c r="P93">
-        <v>-9.555217200000001</v>
+        <v>-9.778406400000001</v>
       </c>
       <c r="Q93">
-        <v>-5.805217200000001</v>
+        <v>-6.028406400000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5768116954079071</v>
+        <v>0.6431881573338958</v>
       </c>
       <c r="T93">
-        <v>8.214582046004081</v>
+        <v>9.241404801754594</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.05295364344995778</v>
+        <v>0.05237806036897999</v>
       </c>
       <c r="W93">
-        <v>0.1901669083952485</v>
+        <v>0.1902824854779088</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5295364344995779</v>
+        <v>0.5237806036897998</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2265149392263878</v>
+        <v>0.2280649392263878</v>
       </c>
       <c r="C94">
-        <v>-56.52012275154209</v>
+        <v>-58.1146184428636</v>
       </c>
       <c r="D94">
-        <v>51.75987724845792</v>
+        <v>51.40038155713641</v>
       </c>
       <c r="E94">
-        <v>65.92</v>
+        <v>67.155</v>
       </c>
       <c r="F94">
-        <v>113.62</v>
+        <v>114.855</v>
       </c>
       <c r="G94">
         <v>5.34</v>
@@ -8995,37 +8995,37 @@
         <v>11.95</v>
       </c>
       <c r="M94">
-        <v>22.814896</v>
+        <v>23.062884</v>
       </c>
       <c r="N94">
-        <v>-10.864896</v>
+        <v>-11.112884</v>
       </c>
       <c r="O94">
-        <v>-1.0864896</v>
+        <v>-1.1112884</v>
       </c>
       <c r="P94">
-        <v>-9.778406400000001</v>
+        <v>-10.0015956</v>
       </c>
       <c r="Q94">
-        <v>-6.028406400000001</v>
+        <v>-6.251595600000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6431881573338958</v>
+        <v>0.7285293226673095</v>
       </c>
       <c r="T94">
-        <v>9.241404801754594</v>
+        <v>10.56160548771954</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.05237806036897999</v>
+        <v>0.0518148554187759</v>
       </c>
       <c r="W94">
-        <v>0.1902824854779088</v>
+        <v>0.1903955770319098</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5237806036897998</v>
+        <v>0.518148554187759</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2280649392263878</v>
+        <v>0.2296149392263878</v>
       </c>
       <c r="C95">
-        <v>-58.1146184428636</v>
+        <v>-59.70415485916737</v>
       </c>
       <c r="D95">
-        <v>51.40038155713641</v>
+        <v>51.04584514083263</v>
       </c>
       <c r="E95">
-        <v>67.155</v>
+        <v>68.39</v>
       </c>
       <c r="F95">
-        <v>114.855</v>
+        <v>116.09</v>
       </c>
       <c r="G95">
         <v>5.34</v>
@@ -9077,37 +9077,37 @@
         <v>11.95</v>
       </c>
       <c r="M95">
-        <v>23.062884</v>
+        <v>23.310872</v>
       </c>
       <c r="N95">
-        <v>-11.112884</v>
+        <v>-11.360872</v>
       </c>
       <c r="O95">
-        <v>-1.1112884</v>
+        <v>-1.1360872</v>
       </c>
       <c r="P95">
-        <v>-10.0015956</v>
+        <v>-10.2247848</v>
       </c>
       <c r="Q95">
-        <v>-6.251595600000002</v>
+        <v>-6.4747848</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7285293226673095</v>
+        <v>0.8423175431118614</v>
       </c>
       <c r="T95">
-        <v>10.56160548771954</v>
+        <v>12.32187306900613</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.0518148554187759</v>
+        <v>0.0512636335526187</v>
       </c>
       <c r="W95">
-        <v>0.1903955770319098</v>
+        <v>0.1905062623826342</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.518148554187759</v>
+        <v>0.5126363355261871</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2296149392263878</v>
+        <v>0.2311649392263878</v>
       </c>
       <c r="C96">
-        <v>-59.70415485916737</v>
+        <v>-61.28883391793272</v>
       </c>
       <c r="D96">
-        <v>51.04584514083263</v>
+        <v>50.69616608206729</v>
       </c>
       <c r="E96">
-        <v>68.39</v>
+        <v>69.625</v>
       </c>
       <c r="F96">
-        <v>116.09</v>
+        <v>117.325</v>
       </c>
       <c r="G96">
         <v>5.34</v>
@@ -9159,37 +9159,37 @@
         <v>11.95</v>
       </c>
       <c r="M96">
-        <v>23.310872</v>
+        <v>23.55886</v>
       </c>
       <c r="N96">
-        <v>-11.360872</v>
+        <v>-11.60886</v>
       </c>
       <c r="O96">
-        <v>-1.1360872</v>
+        <v>-1.160886</v>
       </c>
       <c r="P96">
-        <v>-10.2247848</v>
+        <v>-10.447974</v>
       </c>
       <c r="Q96">
-        <v>-6.4747848</v>
+        <v>-6.697974000000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8423175431118614</v>
+        <v>1.001621051734234</v>
       </c>
       <c r="T96">
-        <v>12.32187306900613</v>
+        <v>14.78624768280736</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.0512636335526187</v>
+        <v>0.05072401635732798</v>
       </c>
       <c r="W96">
-        <v>0.1905062623826342</v>
+        <v>0.1906146175154486</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5126363355261871</v>
+        <v>0.5072401635732797</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2311649392263878</v>
+        <v>0.2327149392263878</v>
       </c>
       <c r="C97">
-        <v>-61.28883391793272</v>
+        <v>-62.86875476298032</v>
       </c>
       <c r="D97">
-        <v>50.69616608206729</v>
+        <v>50.35124523701968</v>
       </c>
       <c r="E97">
-        <v>69.625</v>
+        <v>70.86</v>
       </c>
       <c r="F97">
-        <v>117.325</v>
+        <v>118.56</v>
       </c>
       <c r="G97">
         <v>5.34</v>
@@ -9241,37 +9241,37 @@
         <v>11.95</v>
       </c>
       <c r="M97">
-        <v>23.55886</v>
+        <v>23.806848</v>
       </c>
       <c r="N97">
-        <v>-11.60886</v>
+        <v>-11.856848</v>
       </c>
       <c r="O97">
-        <v>-1.160886</v>
+        <v>-1.1856848</v>
       </c>
       <c r="P97">
-        <v>-10.447974</v>
+        <v>-10.6711632</v>
       </c>
       <c r="Q97">
-        <v>-6.697974000000004</v>
+        <v>-6.921163200000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.001621051734234</v>
+        <v>1.240576314667793</v>
       </c>
       <c r="T97">
-        <v>14.78624768280736</v>
+        <v>18.48280960350921</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.05072401635732798</v>
+        <v>0.05019564118693914</v>
       </c>
       <c r="W97">
-        <v>0.1906146175154486</v>
+        <v>0.1907207152496626</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5072401635732797</v>
+        <v>0.5019564118693914</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2327149392263878</v>
+        <v>0.2685740734711137</v>
       </c>
       <c r="C98">
-        <v>-62.8687547629803</v>
+        <v>-70.9513505656378</v>
       </c>
       <c r="D98">
-        <v>50.3512452370197</v>
+        <v>43.50364943436221</v>
       </c>
       <c r="E98">
-        <v>70.86</v>
+        <v>72.095</v>
       </c>
       <c r="F98">
-        <v>118.56</v>
+        <v>119.795</v>
       </c>
       <c r="G98">
         <v>5.34</v>
@@ -9323,45 +9323,45 @@
         <v>11.95</v>
       </c>
       <c r="M98">
-        <v>23.806848</v>
+        <v>28.247661</v>
       </c>
       <c r="N98">
-        <v>-11.856848</v>
+        <v>-16.297661</v>
       </c>
       <c r="O98">
-        <v>-1.1856848</v>
+        <v>-1.6297661</v>
       </c>
       <c r="P98">
-        <v>-10.6711632</v>
+        <v>-14.6678949</v>
       </c>
       <c r="Q98">
-        <v>-6.921163200000002</v>
+        <v>-10.9178949</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.24057631466779</v>
+        <v>1.650806227714585</v>
       </c>
       <c r="T98">
-        <v>18.48280960350916</v>
+        <v>24.82893588959668</v>
       </c>
       <c r="U98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05019564118693914</v>
+        <v>0.04230438760929622</v>
       </c>
       <c r="W98">
-        <v>0.1907207152496626</v>
+        <v>0.225824625401728</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5019564118693914</v>
+        <v>0.4230438760929621</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2685740734711137</v>
+        <v>0.2704740734711137</v>
       </c>
       <c r="C99">
-        <v>-70.9513505656378</v>
+        <v>-72.49758610225534</v>
       </c>
       <c r="D99">
-        <v>43.50364943436221</v>
+        <v>43.19241389774466</v>
       </c>
       <c r="E99">
-        <v>72.095</v>
+        <v>73.33</v>
       </c>
       <c r="F99">
-        <v>119.795</v>
+        <v>121.03</v>
       </c>
       <c r="G99">
         <v>5.34</v>
@@ -9405,37 +9405,37 @@
         <v>11.95</v>
       </c>
       <c r="M99">
-        <v>28.247661</v>
+        <v>28.538874</v>
       </c>
       <c r="N99">
-        <v>-16.297661</v>
+        <v>-16.588874</v>
       </c>
       <c r="O99">
-        <v>-1.6297661</v>
+        <v>-1.6588874</v>
       </c>
       <c r="P99">
-        <v>-14.6678949</v>
+        <v>-14.9299866</v>
       </c>
       <c r="Q99">
-        <v>-10.9178949</v>
+        <v>-11.1799866</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.650806227714585</v>
+        <v>2.453309341571877</v>
       </c>
       <c r="T99">
-        <v>24.82893588959668</v>
+        <v>37.24340383439501</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04230438760929622</v>
+        <v>0.04187271018471156</v>
       </c>
       <c r="W99">
-        <v>0.225824625401728</v>
+        <v>0.225926414938445</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4230438760929621</v>
+        <v>0.4187271018471156</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2704740734711137</v>
+        <v>0.2723740734711137</v>
       </c>
       <c r="C100">
-        <v>-72.49758610225534</v>
+        <v>-74.03939996531071</v>
       </c>
       <c r="D100">
-        <v>43.19241389774466</v>
+        <v>42.8856000346893</v>
       </c>
       <c r="E100">
-        <v>73.33</v>
+        <v>74.565</v>
       </c>
       <c r="F100">
-        <v>121.03</v>
+        <v>122.265</v>
       </c>
       <c r="G100">
         <v>5.34</v>
@@ -9487,37 +9487,37 @@
         <v>11.95</v>
       </c>
       <c r="M100">
-        <v>28.538874</v>
+        <v>28.830087</v>
       </c>
       <c r="N100">
-        <v>-16.588874</v>
+        <v>-16.880087</v>
       </c>
       <c r="O100">
-        <v>-1.6588874</v>
+        <v>-1.6880087</v>
       </c>
       <c r="P100">
-        <v>-14.9299866</v>
+        <v>-15.1920783</v>
       </c>
       <c r="Q100">
-        <v>-11.1799866</v>
+        <v>-11.4420783</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.453309341571877</v>
+        <v>4.860818683143754</v>
       </c>
       <c r="T100">
-        <v>37.24340383439501</v>
+        <v>74.48680766879004</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04187271018471156</v>
+        <v>0.04144975351617912</v>
       </c>
       <c r="W100">
-        <v>0.225926414938445</v>
+        <v>0.226026148120885</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4187271018471156</v>
+        <v>0.4144975351617911</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2723740734711137</v>
-      </c>
-      <c r="C101">
-        <v>-74.03939996531071</v>
-      </c>
-      <c r="D101">
-        <v>42.8856000346893</v>
-      </c>
-      <c r="E101">
-        <v>74.565</v>
-      </c>
-      <c r="F101">
-        <v>122.265</v>
-      </c>
-      <c r="G101">
-        <v>5.34</v>
-      </c>
-      <c r="H101">
-        <v>75.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>15.7</v>
-      </c>
-      <c r="K101">
-        <v>3.75</v>
-      </c>
-      <c r="L101">
-        <v>11.95</v>
-      </c>
-      <c r="M101">
-        <v>28.830087</v>
-      </c>
-      <c r="N101">
-        <v>-16.880087</v>
-      </c>
-      <c r="O101">
-        <v>-1.6880087</v>
-      </c>
-      <c r="P101">
-        <v>-15.1920783</v>
-      </c>
-      <c r="Q101">
-        <v>-11.4420783</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.860818683143754</v>
-      </c>
-      <c r="T101">
-        <v>74.48680766879004</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04144975351617912</v>
-      </c>
-      <c r="W101">
-        <v>0.226026148120885</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4144975351617911</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
